--- a/inst/testdata/registryid/frs_testpoints_1000.xlsx
+++ b/inst/testdata/registryid/frs_testpoints_1000.xlsx
@@ -371,7 +371,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>110070455604</v>
+        <v>110018797435</v>
       </c>
     </row>
     <row r="3">
@@ -379,7 +379,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>110070488848</v>
+        <v>110035556332</v>
       </c>
     </row>
     <row r="4">
@@ -387,7 +387,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>110071745415</v>
+        <v>110071513252</v>
       </c>
     </row>
     <row r="5">
@@ -395,7 +395,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>110064970946</v>
+        <v>110066558683</v>
       </c>
     </row>
     <row r="6">
@@ -403,7 +403,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>110038198447</v>
+        <v>110005831859</v>
       </c>
     </row>
     <row r="7">
@@ -411,7 +411,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>110067842918</v>
+        <v>110071945465</v>
       </c>
     </row>
     <row r="8">
@@ -419,7 +419,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>110031658329</v>
+        <v>110070469988</v>
       </c>
     </row>
     <row r="9">
@@ -427,7 +427,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>110065730338</v>
+        <v>110070523141</v>
       </c>
     </row>
     <row r="10">
@@ -435,7 +435,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>110066798479</v>
+        <v>110071864051</v>
       </c>
     </row>
     <row r="11">
@@ -443,7 +443,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>110071527082</v>
+        <v>110065032164</v>
       </c>
     </row>
     <row r="12">
@@ -451,7 +451,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>110070425815</v>
+        <v>110038349285</v>
       </c>
     </row>
     <row r="13">
@@ -459,7 +459,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>110070513440</v>
+        <v>110067888183</v>
       </c>
     </row>
     <row r="14">
@@ -467,7 +467,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>110041465615</v>
+        <v>110031683275</v>
       </c>
     </row>
     <row r="15">
@@ -475,7 +475,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>110001888690</v>
+        <v>110065796543</v>
       </c>
     </row>
     <row r="16">
@@ -483,7 +483,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>110062918801</v>
+        <v>110066961265</v>
       </c>
     </row>
     <row r="17">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>110024766895</v>
+        <v>110071727356</v>
       </c>
     </row>
     <row r="18">
@@ -499,7 +499,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>110038007395</v>
+        <v>110070433134</v>
       </c>
     </row>
     <row r="19">
@@ -507,7 +507,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>110030415824</v>
+        <v>110070544780</v>
       </c>
     </row>
     <row r="20">
@@ -515,7 +515,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>110039556511</v>
+        <v>110041581963</v>
       </c>
     </row>
     <row r="21">
@@ -523,7 +523,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>110014779622</v>
+        <v>110001900783</v>
       </c>
     </row>
     <row r="22">
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>110014413312</v>
+        <v>110071977690</v>
       </c>
     </row>
     <row r="23">
@@ -539,7 +539,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>110068343643</v>
+        <v>110063383137</v>
       </c>
     </row>
     <row r="24">
@@ -547,7 +547,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>110071877861</v>
+        <v>110024844169</v>
       </c>
     </row>
     <row r="25">
@@ -555,7 +555,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>110005895870</v>
+        <v>110038238449</v>
       </c>
     </row>
     <row r="26">
@@ -563,7 +563,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>110070535139</v>
+        <v>110030468081</v>
       </c>
     </row>
     <row r="27">
@@ -571,7 +571,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>110070022768</v>
+        <v>110040088428</v>
       </c>
     </row>
     <row r="28">
@@ -579,7 +579,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>110066798371</v>
+        <v>110015335403</v>
       </c>
     </row>
     <row r="29">
@@ -587,7 +587,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>110042097557</v>
+        <v>110014942081</v>
       </c>
     </row>
     <row r="30">
@@ -595,7 +595,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>110006328839</v>
+        <v>110068360605</v>
       </c>
     </row>
     <row r="31">
@@ -603,7 +603,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>110003427104</v>
+        <v>110071932058</v>
       </c>
     </row>
     <row r="32">
@@ -611,7 +611,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>110015474789</v>
+        <v>110006046698</v>
       </c>
     </row>
     <row r="33">
@@ -619,7 +619,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>110040513227</v>
+        <v>110070581162</v>
       </c>
     </row>
     <row r="34">
@@ -627,7 +627,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>110059783186</v>
+        <v>110070001840</v>
       </c>
     </row>
     <row r="35">
@@ -635,7 +635,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>110071374427</v>
+        <v>110066961112</v>
       </c>
     </row>
     <row r="36">
@@ -643,7 +643,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>110065674103</v>
+        <v>110042310594</v>
       </c>
     </row>
     <row r="37">
@@ -651,7 +651,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>110056440953</v>
+        <v>110006474911</v>
       </c>
     </row>
     <row r="38">
@@ -659,7 +659,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>110010103468</v>
+        <v>110003466026</v>
       </c>
     </row>
     <row r="39">
@@ -667,7 +667,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>110045295649</v>
+        <v>110015554559</v>
       </c>
     </row>
     <row r="40">
@@ -675,7 +675,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>110010583485</v>
+        <v>110040741445</v>
       </c>
     </row>
     <row r="41">
@@ -683,7 +683,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>110034830324</v>
+        <v>110060104596</v>
       </c>
     </row>
     <row r="42">
@@ -691,7 +691,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>110015646176</v>
+        <v>110071503961</v>
       </c>
     </row>
     <row r="43">
@@ -699,7 +699,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>110070560633</v>
+        <v>110065741479</v>
       </c>
     </row>
     <row r="44">
@@ -707,7 +707,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>110017095542</v>
+        <v>110057040624</v>
       </c>
     </row>
     <row r="45">
@@ -715,7 +715,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>110070442342</v>
+        <v>110010636277</v>
       </c>
     </row>
     <row r="46">
@@ -723,7 +723,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>110039544721</v>
+        <v>110045519630</v>
       </c>
     </row>
     <row r="47">
@@ -731,7 +731,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>110007447389</v>
+        <v>110010729266</v>
       </c>
     </row>
     <row r="48">
@@ -739,7 +739,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>110070163381</v>
+        <v>110034892819</v>
       </c>
     </row>
     <row r="49">
@@ -747,7 +747,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>110014317284</v>
+        <v>110015862805</v>
       </c>
     </row>
     <row r="50">
@@ -755,7 +755,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>110028189127</v>
+        <v>110070601919</v>
       </c>
     </row>
     <row r="51">
@@ -763,7 +763,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>110063223373</v>
+        <v>110017304816</v>
       </c>
     </row>
     <row r="52">
@@ -771,7 +771,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>110029915661</v>
+        <v>110070453399</v>
       </c>
     </row>
     <row r="53">
@@ -779,7 +779,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>110040402338</v>
+        <v>110040066059</v>
       </c>
     </row>
     <row r="54">
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>110019162715</v>
+        <v>110007835389</v>
       </c>
     </row>
     <row r="55">
@@ -795,7 +795,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>110063010316</v>
+        <v>110070157329</v>
       </c>
     </row>
     <row r="56">
@@ -803,7 +803,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>110070396552</v>
+        <v>110014690557</v>
       </c>
     </row>
     <row r="57">
@@ -811,7 +811,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>110071205680</v>
+        <v>110028222000</v>
       </c>
     </row>
     <row r="58">
@@ -819,7 +819,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>110019171162</v>
+        <v>110063758134</v>
       </c>
     </row>
     <row r="59">
@@ -827,7 +827,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>110013598623</v>
+        <v>110029937460</v>
       </c>
     </row>
     <row r="60">
@@ -835,7 +835,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>110042257152</v>
+        <v>110040655234</v>
       </c>
     </row>
     <row r="61">
@@ -843,7 +843,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>110070457307</v>
+        <v>110019246387</v>
       </c>
     </row>
     <row r="62">
@@ -851,7 +851,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>110032666292</v>
+        <v>110063593133</v>
       </c>
     </row>
     <row r="63">
@@ -859,7 +859,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>110070472799</v>
+        <v>110070398686</v>
       </c>
     </row>
     <row r="64">
@@ -867,7 +867,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>110070342733</v>
+        <v>110071357771</v>
       </c>
     </row>
     <row r="65">
@@ -875,7 +875,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>110014267186</v>
+        <v>110019254643</v>
       </c>
     </row>
     <row r="66">
@@ -883,7 +883,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>110023164083</v>
+        <v>110013842324</v>
       </c>
     </row>
     <row r="67">
@@ -891,7 +891,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>110014406259</v>
+        <v>110042524783</v>
       </c>
     </row>
     <row r="68">
@@ -899,7 +899,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>110071783595</v>
+        <v>110070471822</v>
       </c>
     </row>
     <row r="69">
@@ -907,7 +907,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>110070407595</v>
+        <v>110032861856</v>
       </c>
     </row>
     <row r="70">
@@ -915,7 +915,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>110070343869</v>
+        <v>110070487989</v>
       </c>
     </row>
     <row r="71">
@@ -923,7 +923,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>110030657536</v>
+        <v>110070343159</v>
       </c>
     </row>
     <row r="72">
@@ -931,7 +931,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>110071785771</v>
+        <v>110014387261</v>
       </c>
     </row>
     <row r="73">
@@ -939,7 +939,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>110019698692</v>
+        <v>110024160156</v>
       </c>
     </row>
     <row r="74">
@@ -947,7 +947,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>110038908876</v>
+        <v>110014902383</v>
       </c>
     </row>
     <row r="75">
@@ -955,7 +955,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>110070937429</v>
+        <v>110071881423</v>
       </c>
     </row>
     <row r="76">
@@ -963,7 +963,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>110058779567</v>
+        <v>110070413654</v>
       </c>
     </row>
     <row r="77">
@@ -971,7 +971,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>110041544521</v>
+        <v>110070344348</v>
       </c>
     </row>
     <row r="78">
@@ -979,7 +979,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>110041054042</v>
+        <v>110030677131</v>
       </c>
     </row>
     <row r="79">
@@ -987,7 +987,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>110071503620</v>
+        <v>110071884319</v>
       </c>
     </row>
     <row r="80">
@@ -995,7 +995,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>110014704631</v>
+        <v>110019783714</v>
       </c>
     </row>
     <row r="81">
@@ -1003,7 +1003,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>110057091043</v>
+        <v>110039241692</v>
       </c>
     </row>
     <row r="82">
@@ -1011,7 +1011,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>110071662893</v>
+        <v>110071157106</v>
       </c>
     </row>
     <row r="83">
@@ -1019,7 +1019,7 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>110066323151</v>
+        <v>110059686406</v>
       </c>
     </row>
     <row r="84">
@@ -1027,7 +1027,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>110015567260</v>
+        <v>110041723347</v>
       </c>
     </row>
     <row r="85">
@@ -1035,7 +1035,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>110018574210</v>
+        <v>110041371093</v>
       </c>
     </row>
     <row r="86">
@@ -1043,7 +1043,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>110070525622</v>
+        <v>110071701438</v>
       </c>
     </row>
     <row r="87">
@@ -1051,7 +1051,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>110068441804</v>
+        <v>110015313132</v>
       </c>
     </row>
     <row r="88">
@@ -1059,7 +1059,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>110042001179</v>
+        <v>110058265746</v>
       </c>
     </row>
     <row r="89">
@@ -1067,7 +1067,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>110062897502</v>
+        <v>110071796850</v>
       </c>
     </row>
     <row r="90">
@@ -1075,7 +1075,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>110070467814</v>
+        <v>110066393012</v>
       </c>
     </row>
     <row r="91">
@@ -1083,7 +1083,7 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>110018536333</v>
+        <v>110015783026</v>
       </c>
     </row>
     <row r="92">
@@ -1091,7 +1091,7 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>110069089097</v>
+        <v>110072149316</v>
       </c>
     </row>
     <row r="93">
@@ -1099,7 +1099,7 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>110035333993</v>
+        <v>110018696856</v>
       </c>
     </row>
     <row r="94">
@@ -1107,7 +1107,7 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>110071408344</v>
+        <v>110070566419</v>
       </c>
     </row>
     <row r="95">
@@ -1115,7 +1115,7 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>110006470265</v>
+        <v>110068452294</v>
       </c>
     </row>
     <row r="96">
@@ -1123,7 +1123,7 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>110065362066</v>
+        <v>110042303619</v>
       </c>
     </row>
     <row r="97">
@@ -1131,7 +1131,7 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>110038958697</v>
+        <v>110063332647</v>
       </c>
     </row>
     <row r="98">
@@ -1139,7 +1139,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>110040127671</v>
+        <v>110070482767</v>
       </c>
     </row>
     <row r="99">
@@ -1147,7 +1147,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>110070478053</v>
+        <v>110018662204</v>
       </c>
     </row>
     <row r="100">
@@ -1155,7 +1155,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>110045440313</v>
+        <v>110069048104</v>
       </c>
     </row>
     <row r="101">
@@ -1163,7 +1163,7 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>110025014758</v>
+        <v>110035402089</v>
       </c>
     </row>
     <row r="102">
@@ -1171,7 +1171,7 @@
         <v>101</v>
       </c>
       <c r="B102">
-        <v>110033128425</v>
+        <v>110071536826</v>
       </c>
     </row>
     <row r="103">
@@ -1179,7 +1179,7 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>110071339915</v>
+        <v>110006591964</v>
       </c>
     </row>
     <row r="104">
@@ -1187,7 +1187,7 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>110067978594</v>
+        <v>110065425686</v>
       </c>
     </row>
     <row r="105">
@@ -1195,7 +1195,7 @@
         <v>104</v>
       </c>
       <c r="B105">
-        <v>110044661924</v>
+        <v>110039250039</v>
       </c>
     </row>
     <row r="106">
@@ -1203,7 +1203,7 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>110056247565</v>
+        <v>110040253720</v>
       </c>
     </row>
     <row r="107">
@@ -1211,7 +1211,7 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>110024293496</v>
+        <v>110070502499</v>
       </c>
     </row>
     <row r="108">
@@ -1219,7 +1219,7 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>110002194116</v>
+        <v>110045777272</v>
       </c>
     </row>
     <row r="109">
@@ -1227,7 +1227,7 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>110070405326</v>
+        <v>110025045074</v>
       </c>
     </row>
     <row r="110">
@@ -1235,7 +1235,7 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>110070633689</v>
+        <v>110033193880</v>
       </c>
     </row>
     <row r="111">
@@ -1243,7 +1243,7 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>110071262990</v>
+        <v>110071483911</v>
       </c>
     </row>
     <row r="112">
@@ -1251,7 +1251,7 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>110070536353</v>
+        <v>110068020162</v>
       </c>
     </row>
     <row r="113">
@@ -1259,7 +1259,7 @@
         <v>112</v>
       </c>
       <c r="B113">
-        <v>110070709984</v>
+        <v>110044863564</v>
       </c>
     </row>
     <row r="114">
@@ -1267,7 +1267,7 @@
         <v>113</v>
       </c>
       <c r="B114">
-        <v>110062891633</v>
+        <v>110056429431</v>
       </c>
     </row>
     <row r="115">
@@ -1275,7 +1275,7 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>110056197967</v>
+        <v>110024319673</v>
       </c>
     </row>
     <row r="116">
@@ -1283,7 +1283,7 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>110055825433</v>
+        <v>110002206871</v>
       </c>
     </row>
     <row r="117">
@@ -1291,7 +1291,7 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>110069473493</v>
+        <v>110070411239</v>
       </c>
     </row>
     <row r="118">
@@ -1299,7 +1299,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>110027362921</v>
+        <v>110070787486</v>
       </c>
     </row>
     <row r="119">
@@ -1307,7 +1307,7 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>110017149343</v>
+        <v>110071402197</v>
       </c>
     </row>
     <row r="120">
@@ -1315,7 +1315,7 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>110071720548</v>
+        <v>110070583227</v>
       </c>
     </row>
     <row r="121">
@@ -1323,7 +1323,7 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>110016639413</v>
+        <v>110070916970</v>
       </c>
     </row>
     <row r="122">
@@ -1331,7 +1331,7 @@
         <v>121</v>
       </c>
       <c r="B122">
-        <v>110071083476</v>
+        <v>110063266479</v>
       </c>
     </row>
     <row r="123">
@@ -1339,7 +1339,7 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>110012710263</v>
+        <v>110056336086</v>
       </c>
     </row>
     <row r="124">
@@ -1347,7 +1347,7 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>110059791934</v>
+        <v>110055928956</v>
       </c>
     </row>
     <row r="125">
@@ -1355,7 +1355,7 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>110065386834</v>
+        <v>110069401999</v>
       </c>
     </row>
     <row r="126">
@@ -1363,7 +1363,7 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>110037056565</v>
+        <v>110027859217</v>
       </c>
     </row>
     <row r="127">
@@ -1371,7 +1371,7 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>110024542869</v>
+        <v>110017352283</v>
       </c>
     </row>
     <row r="128">
@@ -1379,7 +1379,7 @@
         <v>127</v>
       </c>
       <c r="B128">
-        <v>110067030625</v>
+        <v>110071841862</v>
       </c>
     </row>
     <row r="129">
@@ -1387,7 +1387,7 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>110003436835</v>
+        <v>110016856892</v>
       </c>
     </row>
     <row r="130">
@@ -1395,7 +1395,7 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>110019188528</v>
+        <v>110071238851</v>
       </c>
     </row>
     <row r="131">
@@ -1403,7 +1403,7 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>110065373072</v>
+        <v>110013241456</v>
       </c>
     </row>
     <row r="132">
@@ -1411,7 +1411,7 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>110070209643</v>
+        <v>110060115726</v>
       </c>
     </row>
     <row r="133">
@@ -1419,7 +1419,7 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>110003549688</v>
+        <v>110065447626</v>
       </c>
     </row>
     <row r="134">
@@ -1427,7 +1427,7 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>110014008572</v>
+        <v>110037217810</v>
       </c>
     </row>
     <row r="135">
@@ -1435,7 +1435,7 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>110034987708</v>
+        <v>110024607834</v>
       </c>
     </row>
     <row r="136">
@@ -1443,7 +1443,7 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>110070686788</v>
+        <v>110067206801</v>
       </c>
     </row>
     <row r="137">
@@ -1451,7 +1451,7 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>110069996269</v>
+        <v>110003475301</v>
       </c>
     </row>
     <row r="138">
@@ -1459,7 +1459,7 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>110015502419</v>
+        <v>110072114143</v>
       </c>
     </row>
     <row r="139">
@@ -1467,7 +1467,7 @@
         <v>138</v>
       </c>
       <c r="B139">
-        <v>110015839501</v>
+        <v>110019271795</v>
       </c>
     </row>
     <row r="140">
@@ -1475,7 +1475,7 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>110042708433</v>
+        <v>110065434630</v>
       </c>
     </row>
     <row r="141">
@@ -1483,7 +1483,7 @@
         <v>140</v>
       </c>
       <c r="B141">
-        <v>110030602649</v>
+        <v>110070202333</v>
       </c>
     </row>
     <row r="142">
@@ -1491,7 +1491,7 @@
         <v>141</v>
       </c>
       <c r="B142">
-        <v>110069606527</v>
+        <v>110003612840</v>
       </c>
     </row>
     <row r="143">
@@ -1499,7 +1499,7 @@
         <v>142</v>
       </c>
       <c r="B143">
-        <v>110004803963</v>
+        <v>110014128504</v>
       </c>
     </row>
     <row r="144">
@@ -1507,7 +1507,7 @@
         <v>143</v>
       </c>
       <c r="B144">
-        <v>110060313511</v>
+        <v>110035064284</v>
       </c>
     </row>
     <row r="145">
@@ -1515,7 +1515,7 @@
         <v>144</v>
       </c>
       <c r="B145">
-        <v>110044562247</v>
+        <v>110070838554</v>
       </c>
     </row>
     <row r="146">
@@ -1523,7 +1523,7 @@
         <v>145</v>
       </c>
       <c r="B146">
-        <v>110015323746</v>
+        <v>110069634872</v>
       </c>
     </row>
     <row r="147">
@@ -1531,7 +1531,7 @@
         <v>146</v>
       </c>
       <c r="B147">
-        <v>110002528300</v>
+        <v>110015591475</v>
       </c>
     </row>
     <row r="148">
@@ -1539,7 +1539,7 @@
         <v>147</v>
       </c>
       <c r="B148">
-        <v>110070526683</v>
+        <v>110016661030</v>
       </c>
     </row>
     <row r="149">
@@ -1547,7 +1547,7 @@
         <v>148</v>
       </c>
       <c r="B149">
-        <v>110066032251</v>
+        <v>110043210959</v>
       </c>
     </row>
     <row r="150">
@@ -1555,7 +1555,7 @@
         <v>149</v>
       </c>
       <c r="B150">
-        <v>110003258439</v>
+        <v>110072160444</v>
       </c>
     </row>
     <row r="151">
@@ -1563,7 +1563,7 @@
         <v>150</v>
       </c>
       <c r="B151">
-        <v>110070166262</v>
+        <v>110030623573</v>
       </c>
     </row>
     <row r="152">
@@ -1571,7 +1571,7 @@
         <v>151</v>
       </c>
       <c r="B152">
-        <v>110019320858</v>
+        <v>110069562878</v>
       </c>
     </row>
     <row r="153">
@@ -1579,7 +1579,7 @@
         <v>152</v>
       </c>
       <c r="B153">
-        <v>110070292570</v>
+        <v>110005011548</v>
       </c>
     </row>
     <row r="154">
@@ -1587,7 +1587,7 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>110002111474</v>
+        <v>110061977268</v>
       </c>
     </row>
     <row r="155">
@@ -1595,7 +1595,7 @@
         <v>154</v>
       </c>
       <c r="B155">
-        <v>110019410412</v>
+        <v>110044751621</v>
       </c>
     </row>
     <row r="156">
@@ -1603,7 +1603,7 @@
         <v>155</v>
       </c>
       <c r="B156">
-        <v>110030504657</v>
+        <v>110015451250</v>
       </c>
     </row>
     <row r="157">
@@ -1611,7 +1611,7 @@
         <v>156</v>
       </c>
       <c r="B157">
-        <v>110017080157</v>
+        <v>110002559231</v>
       </c>
     </row>
     <row r="158">
@@ -1619,7 +1619,7 @@
         <v>157</v>
       </c>
       <c r="B158">
-        <v>110041398396</v>
+        <v>110070568341</v>
       </c>
     </row>
     <row r="159">
@@ -1627,7 +1627,7 @@
         <v>158</v>
       </c>
       <c r="B159">
-        <v>110065808344</v>
+        <v>110066097609</v>
       </c>
     </row>
     <row r="160">
@@ -1635,7 +1635,7 @@
         <v>159</v>
       </c>
       <c r="B160">
-        <v>110031468267</v>
+        <v>110003281289</v>
       </c>
     </row>
     <row r="161">
@@ -1643,7 +1643,7 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>110009619671</v>
+        <v>110070159916</v>
       </c>
     </row>
     <row r="162">
@@ -1651,7 +1651,7 @@
         <v>161</v>
       </c>
       <c r="B162">
-        <v>110070474739</v>
+        <v>110019404081</v>
       </c>
     </row>
     <row r="163">
@@ -1659,7 +1659,7 @@
         <v>162</v>
       </c>
       <c r="B163">
-        <v>110070044315</v>
+        <v>110070292849</v>
       </c>
     </row>
     <row r="164">
@@ -1667,7 +1667,7 @@
         <v>163</v>
       </c>
       <c r="B164">
-        <v>110039322818</v>
+        <v>110002129456</v>
       </c>
     </row>
     <row r="165">
@@ -1675,7 +1675,7 @@
         <v>164</v>
       </c>
       <c r="B165">
-        <v>110044959113</v>
+        <v>110019493528</v>
       </c>
     </row>
     <row r="166">
@@ -1683,7 +1683,7 @@
         <v>165</v>
       </c>
       <c r="B166">
-        <v>110067809562</v>
+        <v>110030526786</v>
       </c>
     </row>
     <row r="167">
@@ -1691,7 +1691,7 @@
         <v>166</v>
       </c>
       <c r="B167">
-        <v>110071864718</v>
+        <v>110017291571</v>
       </c>
     </row>
     <row r="168">
@@ -1699,7 +1699,7 @@
         <v>167</v>
       </c>
       <c r="B168">
-        <v>110011584133</v>
+        <v>110041518890</v>
       </c>
     </row>
     <row r="169">
@@ -1707,7 +1707,7 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>110037821998</v>
+        <v>110065873291</v>
       </c>
     </row>
     <row r="170">
@@ -1715,7 +1715,7 @@
         <v>169</v>
       </c>
       <c r="B170">
-        <v>110029656085</v>
+        <v>110031610692</v>
       </c>
     </row>
     <row r="171">
@@ -1723,7 +1723,7 @@
         <v>170</v>
       </c>
       <c r="B171">
-        <v>110070820462</v>
+        <v>110072030998</v>
       </c>
     </row>
     <row r="172">
@@ -1731,7 +1731,7 @@
         <v>171</v>
       </c>
       <c r="B172">
-        <v>110042570278</v>
+        <v>110009879275</v>
       </c>
     </row>
     <row r="173">
@@ -1739,7 +1739,7 @@
         <v>172</v>
       </c>
       <c r="B173">
-        <v>110008838044</v>
+        <v>110070490154</v>
       </c>
     </row>
     <row r="174">
@@ -1747,7 +1747,7 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>110014385290</v>
+        <v>110070032330</v>
       </c>
     </row>
     <row r="175">
@@ -1755,7 +1755,7 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>110018895016</v>
+        <v>110039415255</v>
       </c>
     </row>
     <row r="176">
@@ -1763,7 +1763,7 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>110001598619</v>
+        <v>110045121872</v>
       </c>
     </row>
     <row r="177">
@@ -1771,7 +1771,7 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>110019111708</v>
+        <v>110067859776</v>
       </c>
     </row>
     <row r="178">
@@ -1779,7 +1779,7 @@
         <v>177</v>
       </c>
       <c r="B178">
-        <v>110029890116</v>
+        <v>110071924553</v>
       </c>
     </row>
     <row r="179">
@@ -1787,7 +1787,7 @@
         <v>178</v>
       </c>
       <c r="B179">
-        <v>110068704085</v>
+        <v>110011771010</v>
       </c>
     </row>
     <row r="180">
@@ -1795,7 +1795,7 @@
         <v>179</v>
       </c>
       <c r="B180">
-        <v>110071726569</v>
+        <v>110037965743</v>
       </c>
     </row>
     <row r="181">
@@ -1803,7 +1803,7 @@
         <v>180</v>
       </c>
       <c r="B181">
-        <v>110056250122</v>
+        <v>110029894363</v>
       </c>
     </row>
     <row r="182">
@@ -1811,7 +1811,7 @@
         <v>181</v>
       </c>
       <c r="B182">
-        <v>110060125582</v>
+        <v>110071041264</v>
       </c>
     </row>
     <row r="183">
@@ -1819,7 +1819,7 @@
         <v>182</v>
       </c>
       <c r="B183">
-        <v>110070458831</v>
+        <v>110042929784</v>
       </c>
     </row>
     <row r="184">
@@ -1827,7 +1827,7 @@
         <v>183</v>
       </c>
       <c r="B184">
-        <v>110010686178</v>
+        <v>110009449169</v>
       </c>
     </row>
     <row r="185">
@@ -1835,7 +1835,7 @@
         <v>184</v>
       </c>
       <c r="B185">
-        <v>110002265325</v>
+        <v>110014860640</v>
       </c>
     </row>
     <row r="186">
@@ -1843,7 +1843,7 @@
         <v>185</v>
       </c>
       <c r="B186">
-        <v>110040734168</v>
+        <v>110019050532</v>
       </c>
     </row>
     <row r="187">
@@ -1851,7 +1851,7 @@
         <v>186</v>
       </c>
       <c r="B187">
-        <v>110020628766</v>
+        <v>110001603168</v>
       </c>
     </row>
     <row r="188">
@@ -1859,7 +1859,7 @@
         <v>187</v>
       </c>
       <c r="B188">
-        <v>110056158839</v>
+        <v>110019195093</v>
       </c>
     </row>
     <row r="189">
@@ -1867,7 +1867,7 @@
         <v>188</v>
       </c>
       <c r="B189">
-        <v>110070412165</v>
+        <v>110029911923</v>
       </c>
     </row>
     <row r="190">
@@ -1875,7 +1875,7 @@
         <v>189</v>
       </c>
       <c r="B190">
-        <v>110063673387</v>
+        <v>110068696799</v>
       </c>
     </row>
     <row r="191">
@@ -1883,7 +1883,7 @@
         <v>190</v>
       </c>
       <c r="B191">
-        <v>110040270159</v>
+        <v>110071847885</v>
       </c>
     </row>
     <row r="192">
@@ -1891,7 +1891,7 @@
         <v>191</v>
       </c>
       <c r="B192">
-        <v>110060151035</v>
+        <v>110056433710</v>
       </c>
     </row>
     <row r="193">
@@ -1899,7 +1899,7 @@
         <v>192</v>
       </c>
       <c r="B193">
-        <v>110024590922</v>
+        <v>110060990968</v>
       </c>
     </row>
     <row r="194">
@@ -1907,7 +1907,7 @@
         <v>193</v>
       </c>
       <c r="B194">
-        <v>110004207983</v>
+        <v>110070473285</v>
       </c>
     </row>
     <row r="195">
@@ -1915,7 +1915,7 @@
         <v>194</v>
       </c>
       <c r="B195">
-        <v>110058575607</v>
+        <v>110010895585</v>
       </c>
     </row>
     <row r="196">
@@ -1923,7 +1923,7 @@
         <v>195</v>
       </c>
       <c r="B196">
-        <v>110066627289</v>
+        <v>110002274574</v>
       </c>
     </row>
     <row r="197">
@@ -1931,7 +1931,7 @@
         <v>196</v>
       </c>
       <c r="B197">
-        <v>110009736465</v>
+        <v>110040988107</v>
       </c>
     </row>
     <row r="198">
@@ -1939,7 +1939,7 @@
         <v>197</v>
       </c>
       <c r="B198">
-        <v>110041010170</v>
+        <v>110020834702</v>
       </c>
     </row>
     <row r="199">
@@ -1947,7 +1947,7 @@
         <v>198</v>
       </c>
       <c r="B199">
-        <v>110037351923</v>
+        <v>110056266286</v>
       </c>
     </row>
     <row r="200">
@@ -1955,7 +1955,7 @@
         <v>199</v>
       </c>
       <c r="B200">
-        <v>110041715953</v>
+        <v>110070418363</v>
       </c>
     </row>
     <row r="201">
@@ -1963,7 +1963,7 @@
         <v>200</v>
       </c>
       <c r="B201">
-        <v>110024429260</v>
+        <v>110063828960</v>
       </c>
     </row>
     <row r="202">
@@ -1971,7 +1971,7 @@
         <v>201</v>
       </c>
       <c r="B202">
-        <v>110065815693</v>
+        <v>110040410926</v>
       </c>
     </row>
     <row r="203">
@@ -1979,7 +1979,7 @@
         <v>202</v>
       </c>
       <c r="B203">
-        <v>110021909808</v>
+        <v>110061057519</v>
       </c>
     </row>
     <row r="204">
@@ -1987,7 +1987,7 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>110070410713</v>
+        <v>110024684386</v>
       </c>
     </row>
     <row r="205">
@@ -1995,7 +1995,7 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>110002349806</v>
+        <v>110004414606</v>
       </c>
     </row>
     <row r="206">
@@ -2003,7 +2003,7 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>110054276939</v>
+        <v>110058775197</v>
       </c>
     </row>
     <row r="207">
@@ -2011,7 +2011,7 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>110071531735</v>
+        <v>110066700537</v>
       </c>
     </row>
     <row r="208">
@@ -2019,7 +2019,7 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>110064896297</v>
+        <v>110010163223</v>
       </c>
     </row>
     <row r="209">
@@ -2027,7 +2027,7 @@
         <v>208</v>
       </c>
       <c r="B209">
-        <v>110011496595</v>
+        <v>110041352461</v>
       </c>
     </row>
     <row r="210">
@@ -2035,7 +2035,7 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>110019682798</v>
+        <v>110037570321</v>
       </c>
     </row>
     <row r="211">
@@ -2043,7 +2043,7 @@
         <v>210</v>
       </c>
       <c r="B211">
-        <v>110070336786</v>
+        <v>110042121888</v>
       </c>
     </row>
     <row r="212">
@@ -2051,7 +2051,7 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>110065147825</v>
+        <v>110024522480</v>
       </c>
     </row>
     <row r="213">
@@ -2059,7 +2059,7 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>110038393869</v>
+        <v>110065881460</v>
       </c>
     </row>
     <row r="214">
@@ -2067,7 +2067,7 @@
         <v>213</v>
       </c>
       <c r="B214">
-        <v>110040045233</v>
+        <v>110022281485</v>
       </c>
     </row>
     <row r="215">
@@ -2075,7 +2075,7 @@
         <v>214</v>
       </c>
       <c r="B215">
-        <v>110033599176</v>
+        <v>110070416900</v>
       </c>
     </row>
     <row r="216">
@@ -2083,7 +2083,7 @@
         <v>215</v>
       </c>
       <c r="B216">
-        <v>110038895176</v>
+        <v>110002374430</v>
       </c>
     </row>
     <row r="217">
@@ -2091,7 +2091,7 @@
         <v>216</v>
       </c>
       <c r="B217">
-        <v>110071879104</v>
+        <v>110054457912</v>
       </c>
     </row>
     <row r="218">
@@ -2099,7 +2099,7 @@
         <v>217</v>
       </c>
       <c r="B218">
-        <v>110058514335</v>
+        <v>110071729776</v>
       </c>
     </row>
     <row r="219">
@@ -2107,7 +2107,7 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>110034241121</v>
+        <v>110064952305</v>
       </c>
     </row>
     <row r="220">
@@ -2115,7 +2115,7 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>110065907987</v>
+        <v>110011680555</v>
       </c>
     </row>
     <row r="221">
@@ -2123,7 +2123,7 @@
         <v>220</v>
       </c>
       <c r="B221">
-        <v>110006347480</v>
+        <v>110019766449</v>
       </c>
     </row>
     <row r="222">
@@ -2131,7 +2131,7 @@
         <v>221</v>
       </c>
       <c r="B222">
-        <v>110070602911</v>
+        <v>110070337202</v>
       </c>
     </row>
     <row r="223">
@@ -2139,7 +2139,7 @@
         <v>222</v>
       </c>
       <c r="B223">
-        <v>110063740215</v>
+        <v>110065204433</v>
       </c>
     </row>
     <row r="224">
@@ -2147,7 +2147,7 @@
         <v>223</v>
       </c>
       <c r="B224">
-        <v>110019172438</v>
+        <v>110038733332</v>
       </c>
     </row>
     <row r="225">
@@ -2155,7 +2155,7 @@
         <v>224</v>
       </c>
       <c r="B225">
-        <v>110058690983</v>
+        <v>110040212427</v>
       </c>
     </row>
     <row r="226">
@@ -2163,7 +2163,7 @@
         <v>225</v>
       </c>
       <c r="B226">
-        <v>110042399883</v>
+        <v>110033636992</v>
       </c>
     </row>
     <row r="227">
@@ -2171,7 +2171,7 @@
         <v>226</v>
       </c>
       <c r="B227">
-        <v>110066370402</v>
+        <v>110039235850</v>
       </c>
     </row>
     <row r="228">
@@ -2179,7 +2179,7 @@
         <v>227</v>
       </c>
       <c r="B228">
-        <v>110008390240</v>
+        <v>110071933460</v>
       </c>
     </row>
     <row r="229">
@@ -2187,7 +2187,7 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>110024363375</v>
+        <v>110058713566</v>
       </c>
     </row>
     <row r="230">
@@ -2195,7 +2195,7 @@
         <v>229</v>
       </c>
       <c r="B230">
-        <v>110037412564</v>
+        <v>110034293048</v>
       </c>
     </row>
     <row r="231">
@@ -2203,7 +2203,7 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>110002162338</v>
+        <v>110065974645</v>
       </c>
     </row>
     <row r="232">
@@ -2211,7 +2211,7 @@
         <v>231</v>
       </c>
       <c r="B232">
-        <v>110038051835</v>
+        <v>110006506539</v>
       </c>
     </row>
     <row r="233">
@@ -2219,7 +2219,7 @@
         <v>232</v>
       </c>
       <c r="B233">
-        <v>110019055993</v>
+        <v>110070698563</v>
       </c>
     </row>
     <row r="234">
@@ -2227,7 +2227,7 @@
         <v>233</v>
       </c>
       <c r="B234">
-        <v>110015924142</v>
+        <v>110063899125</v>
       </c>
     </row>
     <row r="235">
@@ -2235,7 +2235,7 @@
         <v>234</v>
       </c>
       <c r="B235">
-        <v>110019337270</v>
+        <v>110019256017</v>
       </c>
     </row>
     <row r="236">
@@ -2243,7 +2243,7 @@
         <v>235</v>
       </c>
       <c r="B236">
-        <v>110015660373</v>
+        <v>110058897109</v>
       </c>
     </row>
     <row r="237">
@@ -2251,7 +2251,7 @@
         <v>236</v>
       </c>
       <c r="B237">
-        <v>110071070152</v>
+        <v>110042743797</v>
       </c>
     </row>
     <row r="238">
@@ -2259,7 +2259,7 @@
         <v>237</v>
       </c>
       <c r="B238">
-        <v>110066235096</v>
+        <v>110071982377</v>
       </c>
     </row>
     <row r="239">
@@ -2267,7 +2267,7 @@
         <v>238</v>
       </c>
       <c r="B239">
-        <v>110067760220</v>
+        <v>110066440051</v>
       </c>
     </row>
     <row r="240">
@@ -2275,7 +2275,7 @@
         <v>239</v>
       </c>
       <c r="B240">
-        <v>110031703100</v>
+        <v>110008769010</v>
       </c>
     </row>
     <row r="241">
@@ -2283,7 +2283,7 @@
         <v>240</v>
       </c>
       <c r="B241">
-        <v>110015586720</v>
+        <v>110024430784</v>
       </c>
     </row>
     <row r="242">
@@ -2291,7 +2291,7 @@
         <v>241</v>
       </c>
       <c r="B242">
-        <v>110037147192</v>
+        <v>110037706881</v>
       </c>
     </row>
     <row r="243">
@@ -2299,7 +2299,7 @@
         <v>242</v>
       </c>
       <c r="B243">
-        <v>110005514700</v>
+        <v>110002172657</v>
       </c>
     </row>
     <row r="244">
@@ -2307,7 +2307,7 @@
         <v>243</v>
       </c>
       <c r="B244">
-        <v>110065753553</v>
+        <v>110038273533</v>
       </c>
     </row>
     <row r="245">
@@ -2315,7 +2315,7 @@
         <v>244</v>
       </c>
       <c r="B245">
-        <v>110033705630</v>
+        <v>110019139118</v>
       </c>
     </row>
     <row r="246">
@@ -2323,7 +2323,7 @@
         <v>245</v>
       </c>
       <c r="B246">
-        <v>110042338173</v>
+        <v>110016703637</v>
       </c>
     </row>
     <row r="247">
@@ -2331,7 +2331,7 @@
         <v>246</v>
       </c>
       <c r="B247">
-        <v>110070893271</v>
+        <v>110019419912</v>
       </c>
     </row>
     <row r="248">
@@ -2339,7 +2339,7 @@
         <v>247</v>
       </c>
       <c r="B248">
-        <v>110044321089</v>
+        <v>110015899606</v>
       </c>
     </row>
     <row r="249">
@@ -2347,7 +2347,7 @@
         <v>248</v>
       </c>
       <c r="B249">
-        <v>110054247436</v>
+        <v>110071222855</v>
       </c>
     </row>
     <row r="250">
@@ -2355,7 +2355,7 @@
         <v>249</v>
       </c>
       <c r="B250">
-        <v>110070040463</v>
+        <v>110066299598</v>
       </c>
     </row>
     <row r="251">
@@ -2363,7 +2363,7 @@
         <v>250</v>
       </c>
       <c r="B251">
-        <v>110011519856</v>
+        <v>110067818794</v>
       </c>
     </row>
     <row r="252">
@@ -2371,7 +2371,7 @@
         <v>251</v>
       </c>
       <c r="B252">
-        <v>110039357807</v>
+        <v>110031726844</v>
       </c>
     </row>
     <row r="253">
@@ -2379,7 +2379,7 @@
         <v>252</v>
       </c>
       <c r="B253">
-        <v>110041066360</v>
+        <v>110071953707</v>
       </c>
     </row>
     <row r="254">
@@ -2387,7 +2387,7 @@
         <v>253</v>
       </c>
       <c r="B254">
-        <v>110017461977</v>
+        <v>110015823509</v>
       </c>
     </row>
     <row r="255">
@@ -2395,7 +2395,7 @@
         <v>254</v>
       </c>
       <c r="B255">
-        <v>110070411699</v>
+        <v>110037295049</v>
       </c>
     </row>
     <row r="256">
@@ -2403,7 +2403,7 @@
         <v>255</v>
       </c>
       <c r="B256">
-        <v>110014116250</v>
+        <v>110005728187</v>
       </c>
     </row>
     <row r="257">
@@ -2411,7 +2411,7 @@
         <v>256</v>
       </c>
       <c r="B257">
-        <v>110042810152</v>
+        <v>110065820017</v>
       </c>
     </row>
     <row r="258">
@@ -2419,7 +2419,7 @@
         <v>257</v>
       </c>
       <c r="B258">
-        <v>110066176426</v>
+        <v>110033755657</v>
       </c>
     </row>
     <row r="259">
@@ -2427,7 +2427,7 @@
         <v>258</v>
       </c>
       <c r="B259">
-        <v>110071089600</v>
+        <v>110042691833</v>
       </c>
     </row>
     <row r="260">
@@ -2435,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="B260">
-        <v>110012022122</v>
+        <v>110071999927</v>
       </c>
     </row>
     <row r="261">
@@ -2443,7 +2443,7 @@
         <v>260</v>
       </c>
       <c r="B261">
-        <v>110070512411</v>
+        <v>110071132283</v>
       </c>
     </row>
     <row r="262">
@@ -2451,7 +2451,7 @@
         <v>261</v>
       </c>
       <c r="B262">
-        <v>110070912580</v>
+        <v>110044505112</v>
       </c>
     </row>
     <row r="263">
@@ -2459,7 +2459,7 @@
         <v>262</v>
       </c>
       <c r="B263">
-        <v>110028278851</v>
+        <v>110054385278</v>
       </c>
     </row>
     <row r="264">
@@ -2467,7 +2467,7 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>110015307719</v>
+        <v>110070024551</v>
       </c>
     </row>
     <row r="265">
@@ -2475,7 +2475,7 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>110002702004</v>
+        <v>110011705039</v>
       </c>
     </row>
     <row r="266">
@@ -2483,7 +2483,7 @@
         <v>265</v>
       </c>
       <c r="B266">
-        <v>110060430984</v>
+        <v>110039450215</v>
       </c>
     </row>
     <row r="267">
@@ -2491,7 +2491,7 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>110070473003</v>
+        <v>110041373938</v>
       </c>
     </row>
     <row r="268">
@@ -2499,7 +2499,7 @@
         <v>267</v>
       </c>
       <c r="B268">
-        <v>110060277454</v>
+        <v>110017563046</v>
       </c>
     </row>
     <row r="269">
@@ -2507,7 +2507,7 @@
         <v>268</v>
       </c>
       <c r="B269">
-        <v>110024278468</v>
+        <v>110070417902</v>
       </c>
     </row>
     <row r="270">
@@ -2515,7 +2515,7 @@
         <v>269</v>
       </c>
       <c r="B270">
-        <v>110012988981</v>
+        <v>110014195174</v>
       </c>
     </row>
     <row r="271">
@@ -2523,7 +2523,7 @@
         <v>270</v>
       </c>
       <c r="B271">
-        <v>110070459991</v>
+        <v>110043335183</v>
       </c>
     </row>
     <row r="272">
@@ -2531,7 +2531,7 @@
         <v>271</v>
       </c>
       <c r="B272">
-        <v>110070561535</v>
+        <v>110066242060</v>
       </c>
     </row>
     <row r="273">
@@ -2539,7 +2539,7 @@
         <v>272</v>
       </c>
       <c r="B273">
-        <v>110025099738</v>
+        <v>110071251285</v>
       </c>
     </row>
     <row r="274">
@@ -2547,7 +2547,7 @@
         <v>273</v>
       </c>
       <c r="B274">
-        <v>110070251259</v>
+        <v>110012165986</v>
       </c>
     </row>
     <row r="275">
@@ -2555,7 +2555,7 @@
         <v>274</v>
       </c>
       <c r="B275">
-        <v>110070578229</v>
+        <v>110070541263</v>
       </c>
     </row>
     <row r="276">
@@ -2563,7 +2563,7 @@
         <v>275</v>
       </c>
       <c r="B276">
-        <v>110070282201</v>
+        <v>110071140174</v>
       </c>
     </row>
     <row r="277">
@@ -2571,7 +2571,7 @@
         <v>276</v>
       </c>
       <c r="B277">
-        <v>110019401707</v>
+        <v>110028873654</v>
       </c>
     </row>
     <row r="278">
@@ -2579,7 +2579,7 @@
         <v>277</v>
       </c>
       <c r="B278">
-        <v>110070213417</v>
+        <v>110015445632</v>
       </c>
     </row>
     <row r="279">
@@ -2587,7 +2587,7 @@
         <v>278</v>
       </c>
       <c r="B279">
-        <v>110071827311</v>
+        <v>110002717025</v>
       </c>
     </row>
     <row r="280">
@@ -2595,7 +2595,7 @@
         <v>279</v>
       </c>
       <c r="B280">
-        <v>110071347376</v>
+        <v>110062638285</v>
       </c>
     </row>
     <row r="281">
@@ -2603,7 +2603,7 @@
         <v>280</v>
       </c>
       <c r="B281">
-        <v>110011646264</v>
+        <v>110070488213</v>
       </c>
     </row>
     <row r="282">
@@ -2611,7 +2611,7 @@
         <v>281</v>
       </c>
       <c r="B282">
-        <v>110065524454</v>
+        <v>110061470974</v>
       </c>
     </row>
     <row r="283">
@@ -2619,7 +2619,7 @@
         <v>282</v>
       </c>
       <c r="B283">
-        <v>110003258251</v>
+        <v>110024310128</v>
       </c>
     </row>
     <row r="284">
@@ -2627,7 +2627,7 @@
         <v>283</v>
       </c>
       <c r="B284">
-        <v>110070043985</v>
+        <v>110013317302</v>
       </c>
     </row>
     <row r="285">
@@ -2635,7 +2635,7 @@
         <v>284</v>
       </c>
       <c r="B285">
-        <v>110018668681</v>
+        <v>110070474498</v>
       </c>
     </row>
     <row r="286">
@@ -2643,7 +2643,7 @@
         <v>285</v>
       </c>
       <c r="B286">
-        <v>110030910361</v>
+        <v>110070602731</v>
       </c>
     </row>
     <row r="287">
@@ -2651,7 +2651,7 @@
         <v>286</v>
       </c>
       <c r="B287">
-        <v>110055071997</v>
+        <v>110025128289</v>
       </c>
     </row>
     <row r="288">
@@ -2659,7 +2659,7 @@
         <v>287</v>
       </c>
       <c r="B288">
-        <v>110025324593</v>
+        <v>110070248299</v>
       </c>
     </row>
     <row r="289">
@@ -2667,7 +2667,7 @@
         <v>288</v>
       </c>
       <c r="B289">
-        <v>110071808413</v>
+        <v>110072052930</v>
       </c>
     </row>
     <row r="290">
@@ -2675,7 +2675,7 @@
         <v>289</v>
       </c>
       <c r="B290">
-        <v>110004027277</v>
+        <v>110070624692</v>
       </c>
     </row>
     <row r="291">
@@ -2683,7 +2683,7 @@
         <v>290</v>
       </c>
       <c r="B291">
-        <v>110065655142</v>
+        <v>110070282426</v>
       </c>
     </row>
     <row r="292">
@@ -2691,7 +2691,7 @@
         <v>291</v>
       </c>
       <c r="B292">
-        <v>110070061891</v>
+        <v>110019484501</v>
       </c>
     </row>
     <row r="293">
@@ -2699,7 +2699,7 @@
         <v>292</v>
       </c>
       <c r="B293">
-        <v>110029922387</v>
+        <v>110070207891</v>
       </c>
     </row>
     <row r="294">
@@ -2707,7 +2707,7 @@
         <v>293</v>
       </c>
       <c r="B294">
-        <v>110017148852</v>
+        <v>110072084757</v>
       </c>
     </row>
     <row r="295">
@@ -2715,7 +2715,7 @@
         <v>294</v>
       </c>
       <c r="B295">
-        <v>110041350436</v>
+        <v>110071912103</v>
       </c>
     </row>
     <row r="296">
@@ -2723,7 +2723,7 @@
         <v>295</v>
       </c>
       <c r="B296">
-        <v>110032888659</v>
+        <v>110071487570</v>
       </c>
     </row>
     <row r="297">
@@ -2731,7 +2731,7 @@
         <v>296</v>
       </c>
       <c r="B297">
-        <v>110044577035</v>
+        <v>110011837502</v>
       </c>
     </row>
     <row r="298">
@@ -2739,7 +2739,7 @@
         <v>297</v>
       </c>
       <c r="B298">
-        <v>110055686574</v>
+        <v>110065592120</v>
       </c>
     </row>
     <row r="299">
@@ -2747,7 +2747,7 @@
         <v>298</v>
       </c>
       <c r="B299">
-        <v>110071297694</v>
+        <v>110003281038</v>
       </c>
     </row>
     <row r="300">
@@ -2755,7 +2755,7 @@
         <v>299</v>
       </c>
       <c r="B300">
-        <v>110003137864</v>
+        <v>110070031607</v>
       </c>
     </row>
     <row r="301">
@@ -2763,7 +2763,7 @@
         <v>300</v>
       </c>
       <c r="B301">
-        <v>110071862962</v>
+        <v>110018784724</v>
       </c>
     </row>
     <row r="302">
@@ -2771,7 +2771,7 @@
         <v>301</v>
       </c>
       <c r="B302">
-        <v>110070666857</v>
+        <v>110031020124</v>
       </c>
     </row>
     <row r="303">
@@ -2779,7 +2779,7 @@
         <v>302</v>
       </c>
       <c r="B303">
-        <v>110005233924</v>
+        <v>110055235963</v>
       </c>
     </row>
     <row r="304">
@@ -2787,7 +2787,7 @@
         <v>303</v>
       </c>
       <c r="B304">
-        <v>110070065028</v>
+        <v>110025385580</v>
       </c>
     </row>
     <row r="305">
@@ -2795,7 +2795,7 @@
         <v>304</v>
       </c>
       <c r="B305">
-        <v>110003114683</v>
+        <v>110071896392</v>
       </c>
     </row>
     <row r="306">
@@ -2803,7 +2803,7 @@
         <v>305</v>
       </c>
       <c r="B306">
-        <v>110005213848</v>
+        <v>110004136355</v>
       </c>
     </row>
     <row r="307">
@@ -2811,7 +2811,7 @@
         <v>306</v>
       </c>
       <c r="B307">
-        <v>110071293424</v>
+        <v>110065719672</v>
       </c>
     </row>
     <row r="308">
@@ -2819,7 +2819,7 @@
         <v>307</v>
       </c>
       <c r="B308">
-        <v>110046369782</v>
+        <v>110070047645</v>
       </c>
     </row>
     <row r="309">
@@ -2827,7 +2827,7 @@
         <v>308</v>
       </c>
       <c r="B309">
-        <v>110066578055</v>
+        <v>110029944292</v>
       </c>
     </row>
     <row r="310">
@@ -2835,7 +2835,7 @@
         <v>309</v>
       </c>
       <c r="B310">
-        <v>110031462744</v>
+        <v>110017350123</v>
       </c>
     </row>
     <row r="311">
@@ -2843,7 +2843,7 @@
         <v>310</v>
       </c>
       <c r="B311">
-        <v>110028208124</v>
+        <v>110041472947</v>
       </c>
     </row>
     <row r="312">
@@ -2851,7 +2851,7 @@
         <v>311</v>
       </c>
       <c r="B312">
-        <v>110015601847</v>
+        <v>110032965762</v>
       </c>
     </row>
     <row r="313">
@@ -2859,7 +2859,7 @@
         <v>312</v>
       </c>
       <c r="B313">
-        <v>110043872164</v>
+        <v>110044761335</v>
       </c>
     </row>
     <row r="314">
@@ -2867,7 +2867,7 @@
         <v>313</v>
       </c>
       <c r="B314">
-        <v>110011023472</v>
+        <v>110055789767</v>
       </c>
     </row>
     <row r="315">
@@ -2875,7 +2875,7 @@
         <v>314</v>
       </c>
       <c r="B315">
-        <v>110001949330</v>
+        <v>110071445645</v>
       </c>
     </row>
     <row r="316">
@@ -2883,7 +2883,7 @@
         <v>315</v>
       </c>
       <c r="B316">
-        <v>110032508542</v>
+        <v>110003174038</v>
       </c>
     </row>
     <row r="317">
@@ -2891,7 +2891,7 @@
         <v>316</v>
       </c>
       <c r="B317">
-        <v>110064936896</v>
+        <v>110071922676</v>
       </c>
     </row>
     <row r="318">
@@ -2899,7 +2899,7 @@
         <v>317</v>
       </c>
       <c r="B318">
-        <v>110034822039</v>
+        <v>110070818724</v>
       </c>
     </row>
     <row r="319">
@@ -2907,7 +2907,7 @@
         <v>318</v>
       </c>
       <c r="B319">
-        <v>110070526383</v>
+        <v>110005440549</v>
       </c>
     </row>
     <row r="320">
@@ -2915,7 +2915,7 @@
         <v>319</v>
       </c>
       <c r="B320">
-        <v>110030657787</v>
+        <v>110070050914</v>
       </c>
     </row>
     <row r="321">
@@ -2923,7 +2923,7 @@
         <v>320</v>
       </c>
       <c r="B321">
-        <v>110065623347</v>
+        <v>110003149272</v>
       </c>
     </row>
     <row r="322">
@@ -2931,7 +2931,7 @@
         <v>321</v>
       </c>
       <c r="B322">
-        <v>110071146859</v>
+        <v>110005427831</v>
       </c>
     </row>
     <row r="323">
@@ -2939,7 +2939,7 @@
         <v>322</v>
       </c>
       <c r="B323">
-        <v>110038362759</v>
+        <v>110071438476</v>
       </c>
     </row>
     <row r="324">
@@ -2947,7 +2947,7 @@
         <v>323</v>
       </c>
       <c r="B324">
-        <v>110070030099</v>
+        <v>110046551192</v>
       </c>
     </row>
     <row r="325">
@@ -2955,7 +2955,7 @@
         <v>324</v>
       </c>
       <c r="B325">
-        <v>110029984186</v>
+        <v>110066648658</v>
       </c>
     </row>
     <row r="326">
@@ -2963,7 +2963,7 @@
         <v>325</v>
       </c>
       <c r="B326">
-        <v>110071861768</v>
+        <v>110031607072</v>
       </c>
     </row>
     <row r="327">
@@ -2971,7 +2971,7 @@
         <v>326</v>
       </c>
       <c r="B327">
-        <v>110070400271</v>
+        <v>110028235880</v>
       </c>
     </row>
     <row r="328">
@@ -2979,7 +2979,7 @@
         <v>327</v>
       </c>
       <c r="B328">
-        <v>110068406790</v>
+        <v>110015838511</v>
       </c>
     </row>
     <row r="329">
@@ -2987,7 +2987,7 @@
         <v>328</v>
       </c>
       <c r="B329">
-        <v>110034988280</v>
+        <v>110044134013</v>
       </c>
     </row>
     <row r="330">
@@ -2995,7 +2995,7 @@
         <v>329</v>
       </c>
       <c r="B330">
-        <v>110055834432</v>
+        <v>110011494276</v>
       </c>
     </row>
     <row r="331">
@@ -3003,7 +3003,7 @@
         <v>330</v>
       </c>
       <c r="B331">
-        <v>110066075240</v>
+        <v>110001970305</v>
       </c>
     </row>
     <row r="332">
@@ -3011,7 +3011,7 @@
         <v>331</v>
       </c>
       <c r="B332">
-        <v>110071656793</v>
+        <v>110032530125</v>
       </c>
     </row>
     <row r="333">
@@ -3019,7 +3019,7 @@
         <v>332</v>
       </c>
       <c r="B333">
-        <v>110065635600</v>
+        <v>110064991399</v>
       </c>
     </row>
     <row r="334">
@@ -3027,7 +3027,7 @@
         <v>333</v>
       </c>
       <c r="B334">
-        <v>110071294607</v>
+        <v>110034883632</v>
       </c>
     </row>
     <row r="335">
@@ -3035,7 +3035,7 @@
         <v>334</v>
       </c>
       <c r="B335">
-        <v>110070079555</v>
+        <v>110070567804</v>
       </c>
     </row>
     <row r="336">
@@ -3043,7 +3043,7 @@
         <v>335</v>
       </c>
       <c r="B336">
-        <v>110070465374</v>
+        <v>110030677391</v>
       </c>
     </row>
     <row r="337">
@@ -3051,7 +3051,7 @@
         <v>336</v>
       </c>
       <c r="B337">
-        <v>110024595678</v>
+        <v>110065680944</v>
       </c>
     </row>
     <row r="338">
@@ -3059,7 +3059,7 @@
         <v>337</v>
       </c>
       <c r="B338">
-        <v>110025369090</v>
+        <v>110071298301</v>
       </c>
     </row>
     <row r="339">
@@ -3067,7 +3067,7 @@
         <v>338</v>
       </c>
       <c r="B339">
-        <v>110070345719</v>
+        <v>110038725476</v>
       </c>
     </row>
     <row r="340">
@@ -3075,7 +3075,7 @@
         <v>339</v>
       </c>
       <c r="B340">
-        <v>110019031750</v>
+        <v>110071999771</v>
       </c>
     </row>
     <row r="341">
@@ -3083,7 +3083,7 @@
         <v>340</v>
       </c>
       <c r="B341">
-        <v>110001378456</v>
+        <v>110070011006</v>
       </c>
     </row>
     <row r="342">
@@ -3091,7 +3091,7 @@
         <v>341</v>
       </c>
       <c r="B342">
-        <v>110002774338</v>
+        <v>110030004849</v>
       </c>
     </row>
     <row r="343">
@@ -3099,7 +3099,7 @@
         <v>342</v>
       </c>
       <c r="B343">
-        <v>110070106031</v>
+        <v>110071921958</v>
       </c>
     </row>
     <row r="344">
@@ -3107,7 +3107,7 @@
         <v>343</v>
       </c>
       <c r="B344">
-        <v>110011727621</v>
+        <v>110070404340</v>
       </c>
     </row>
     <row r="345">
@@ -3115,7 +3115,7 @@
         <v>344</v>
       </c>
       <c r="B345">
-        <v>110040758882</v>
+        <v>110068421121</v>
       </c>
     </row>
     <row r="346">
@@ -3123,7 +3123,7 @@
         <v>345</v>
       </c>
       <c r="B346">
-        <v>110006668935</v>
+        <v>110035064952</v>
       </c>
     </row>
     <row r="347">
@@ -3131,7 +3131,7 @@
         <v>346</v>
       </c>
       <c r="B347">
-        <v>110065695625</v>
+        <v>110055954436</v>
       </c>
     </row>
     <row r="348">
@@ -3139,7 +3139,7 @@
         <v>347</v>
       </c>
       <c r="B348">
-        <v>110012104748</v>
+        <v>110066142588</v>
       </c>
     </row>
     <row r="349">
@@ -3147,7 +3147,7 @@
         <v>348</v>
       </c>
       <c r="B349">
-        <v>110068491439</v>
+        <v>110071778943</v>
       </c>
     </row>
     <row r="350">
@@ -3155,7 +3155,7 @@
         <v>349</v>
       </c>
       <c r="B350">
-        <v>110070445660</v>
+        <v>110072091200</v>
       </c>
     </row>
     <row r="351">
@@ -3163,7 +3163,7 @@
         <v>350</v>
       </c>
       <c r="B351">
-        <v>110055591195</v>
+        <v>110065695411</v>
       </c>
     </row>
     <row r="352">
@@ -3171,7 +3171,7 @@
         <v>351</v>
       </c>
       <c r="B352">
-        <v>110040644023</v>
+        <v>110071442228</v>
       </c>
     </row>
     <row r="353">
@@ -3179,7 +3179,7 @@
         <v>352</v>
       </c>
       <c r="B353">
-        <v>110036151589</v>
+        <v>110072145715</v>
       </c>
     </row>
     <row r="354">
@@ -3187,7 +3187,7 @@
         <v>353</v>
       </c>
       <c r="B354">
-        <v>110071356533</v>
+        <v>110070060722</v>
       </c>
     </row>
     <row r="355">
@@ -3195,7 +3195,7 @@
         <v>354</v>
       </c>
       <c r="B355">
-        <v>110018432463</v>
+        <v>110071965034</v>
       </c>
     </row>
     <row r="356">
@@ -3203,7 +3203,7 @@
         <v>355</v>
       </c>
       <c r="B356">
-        <v>110037738428</v>
+        <v>110072117853</v>
       </c>
     </row>
     <row r="357">
@@ -3211,7 +3211,7 @@
         <v>356</v>
       </c>
       <c r="B357">
-        <v>110070329165</v>
+        <v>110070480258</v>
       </c>
     </row>
     <row r="358">
@@ -3219,7 +3219,7 @@
         <v>357</v>
       </c>
       <c r="B358">
-        <v>110005210244</v>
+        <v>110024696104</v>
       </c>
     </row>
     <row r="359">
@@ -3227,7 +3227,7 @@
         <v>358</v>
       </c>
       <c r="B359">
-        <v>110012825586</v>
+        <v>110026553254</v>
       </c>
     </row>
     <row r="360">
@@ -3235,7 +3235,7 @@
         <v>359</v>
       </c>
       <c r="B360">
-        <v>110012116771</v>
+        <v>110070346173</v>
       </c>
     </row>
     <row r="361">
@@ -3243,7 +3243,7 @@
         <v>360</v>
       </c>
       <c r="B361">
-        <v>110071307508</v>
+        <v>110072151521</v>
       </c>
     </row>
     <row r="362">
@@ -3251,7 +3251,7 @@
         <v>361</v>
       </c>
       <c r="B362">
-        <v>110071380995</v>
+        <v>110019114395</v>
       </c>
     </row>
     <row r="363">
@@ -3259,7 +3259,7 @@
         <v>362</v>
       </c>
       <c r="B363">
-        <v>110070219616</v>
+        <v>110001379437</v>
       </c>
     </row>
     <row r="364">
@@ -3267,7 +3267,7 @@
         <v>363</v>
       </c>
       <c r="B364">
-        <v>110070556223</v>
+        <v>110002787798</v>
       </c>
     </row>
     <row r="365">
@@ -3275,7 +3275,7 @@
         <v>364</v>
       </c>
       <c r="B365">
-        <v>110071871788</v>
+        <v>110070093664</v>
       </c>
     </row>
     <row r="366">
@@ -3283,7 +3283,7 @@
         <v>365</v>
       </c>
       <c r="B366">
-        <v>110071776017</v>
+        <v>110011928361</v>
       </c>
     </row>
     <row r="367">
@@ -3291,7 +3291,7 @@
         <v>366</v>
       </c>
       <c r="B367">
-        <v>110070120139</v>
+        <v>110041014023</v>
       </c>
     </row>
     <row r="368">
@@ -3299,7 +3299,7 @@
         <v>367</v>
       </c>
       <c r="B368">
-        <v>110055601585</v>
+        <v>110006884443</v>
       </c>
     </row>
     <row r="369">
@@ -3307,7 +3307,7 @@
         <v>368</v>
       </c>
       <c r="B369">
-        <v>110042674219</v>
+        <v>110065762721</v>
       </c>
     </row>
     <row r="370">
@@ -3315,7 +3315,7 @@
         <v>369</v>
       </c>
       <c r="B370">
-        <v>110071881724</v>
+        <v>110012311122</v>
       </c>
     </row>
     <row r="371">
@@ -3323,7 +3323,7 @@
         <v>370</v>
       </c>
       <c r="B371">
-        <v>110032245023</v>
+        <v>110068497406</v>
       </c>
     </row>
     <row r="372">
@@ -3331,7 +3331,7 @@
         <v>371</v>
       </c>
       <c r="B372">
-        <v>110002403471</v>
+        <v>110070456847</v>
       </c>
     </row>
     <row r="373">
@@ -3339,7 +3339,7 @@
         <v>372</v>
       </c>
       <c r="B373">
-        <v>110070903746</v>
+        <v>110055720313</v>
       </c>
     </row>
     <row r="374">
@@ -3347,7 +3347,7 @@
         <v>373</v>
       </c>
       <c r="B374">
-        <v>110036226367</v>
+        <v>110040808472</v>
       </c>
     </row>
     <row r="375">
@@ -3355,7 +3355,7 @@
         <v>374</v>
       </c>
       <c r="B375">
-        <v>110045542061</v>
+        <v>110036222502</v>
       </c>
     </row>
     <row r="376">
@@ -3363,7 +3363,7 @@
         <v>375</v>
       </c>
       <c r="B376">
-        <v>110070600767</v>
+        <v>110071490376</v>
       </c>
     </row>
     <row r="377">
@@ -3371,7 +3371,7 @@
         <v>376</v>
       </c>
       <c r="B377">
-        <v>110008057048</v>
+        <v>110018555838</v>
       </c>
     </row>
     <row r="378">
@@ -3379,7 +3379,7 @@
         <v>377</v>
       </c>
       <c r="B378">
-        <v>110014116839</v>
+        <v>110037812052</v>
       </c>
     </row>
     <row r="379">
@@ -3387,7 +3387,7 @@
         <v>378</v>
       </c>
       <c r="B379">
-        <v>110070335449</v>
+        <v>110070329535</v>
       </c>
     </row>
     <row r="380">
@@ -3395,7 +3395,7 @@
         <v>379</v>
       </c>
       <c r="B380">
-        <v>110019516594</v>
+        <v>110005423755</v>
       </c>
     </row>
     <row r="381">
@@ -3403,7 +3403,7 @@
         <v>380</v>
       </c>
       <c r="B381">
-        <v>110070517621</v>
+        <v>110013273135</v>
       </c>
     </row>
     <row r="382">
@@ -3411,7 +3411,7 @@
         <v>381</v>
       </c>
       <c r="B382">
-        <v>110018331624</v>
+        <v>110012352202</v>
       </c>
     </row>
     <row r="383">
@@ -3419,7 +3419,7 @@
         <v>382</v>
       </c>
       <c r="B383">
-        <v>110055538850</v>
+        <v>110071448539</v>
       </c>
     </row>
     <row r="384">
@@ -3427,7 +3427,7 @@
         <v>383</v>
       </c>
       <c r="B384">
-        <v>110046279460</v>
+        <v>110071509450</v>
       </c>
     </row>
     <row r="385">
@@ -3435,7 +3435,7 @@
         <v>384</v>
       </c>
       <c r="B385">
-        <v>110070459254</v>
+        <v>110070214677</v>
       </c>
     </row>
     <row r="386">
@@ -3443,7 +3443,7 @@
         <v>385</v>
       </c>
       <c r="B386">
-        <v>110006529907</v>
+        <v>110070598256</v>
       </c>
     </row>
     <row r="387">
@@ -3451,7 +3451,7 @@
         <v>386</v>
       </c>
       <c r="B387">
-        <v>110046512519</v>
+        <v>110071930105</v>
       </c>
     </row>
     <row r="388">
@@ -3459,7 +3459,7 @@
         <v>387</v>
       </c>
       <c r="B388">
-        <v>110017467579</v>
+        <v>110071876173</v>
       </c>
     </row>
     <row r="389">
@@ -3467,7 +3467,7 @@
         <v>388</v>
       </c>
       <c r="B389">
-        <v>110071102313</v>
+        <v>110070101704</v>
       </c>
     </row>
     <row r="390">
@@ -3475,7 +3475,7 @@
         <v>389</v>
       </c>
       <c r="B390">
-        <v>110034375147</v>
+        <v>110055728191</v>
       </c>
     </row>
     <row r="391">
@@ -3483,7 +3483,7 @@
         <v>390</v>
       </c>
       <c r="B391">
-        <v>110059743666</v>
+        <v>110043178236</v>
       </c>
     </row>
     <row r="392">
@@ -3491,7 +3491,7 @@
         <v>391</v>
       </c>
       <c r="B392">
-        <v>110065309829</v>
+        <v>110071939315</v>
       </c>
     </row>
     <row r="393">
@@ -3499,7 +3499,7 @@
         <v>392</v>
       </c>
       <c r="B393">
-        <v>110031922551</v>
+        <v>110032266704</v>
       </c>
     </row>
     <row r="394">
@@ -3507,7 +3507,7 @@
         <v>393</v>
       </c>
       <c r="B394">
-        <v>110056122538</v>
+        <v>110002429729</v>
       </c>
     </row>
     <row r="395">
@@ -3515,7 +3515,7 @@
         <v>394</v>
       </c>
       <c r="B395">
-        <v>110040103768</v>
+        <v>110071136409</v>
       </c>
     </row>
     <row r="396">
@@ -3523,7 +3523,7 @@
         <v>395</v>
       </c>
       <c r="B396">
-        <v>110070612853</v>
+        <v>110071977650</v>
       </c>
     </row>
     <row r="397">
@@ -3531,7 +3531,7 @@
         <v>396</v>
       </c>
       <c r="B397">
-        <v>110028145246</v>
+        <v>110036299092</v>
       </c>
     </row>
     <row r="398">
@@ -3539,7 +3539,7 @@
         <v>397</v>
       </c>
       <c r="B398">
-        <v>110032381474</v>
+        <v>110045835405</v>
       </c>
     </row>
     <row r="399">
@@ -3547,7 +3547,7 @@
         <v>398</v>
       </c>
       <c r="B399">
-        <v>110001088938</v>
+        <v>110070695800</v>
       </c>
     </row>
     <row r="400">
@@ -3555,7 +3555,7 @@
         <v>399</v>
       </c>
       <c r="B400">
-        <v>110070214268</v>
+        <v>110008383882</v>
       </c>
     </row>
     <row r="401">
@@ -3563,7 +3563,7 @@
         <v>400</v>
       </c>
       <c r="B401">
-        <v>110038720088</v>
+        <v>110014195780</v>
       </c>
     </row>
     <row r="402">
@@ -3571,7 +3571,7 @@
         <v>401</v>
       </c>
       <c r="B402">
-        <v>110029955813</v>
+        <v>110070335864</v>
       </c>
     </row>
     <row r="403">
@@ -3579,7 +3579,7 @@
         <v>402</v>
       </c>
       <c r="B403">
-        <v>110024966955</v>
+        <v>110019598693</v>
       </c>
     </row>
     <row r="404">
@@ -3587,7 +3587,7 @@
         <v>403</v>
       </c>
       <c r="B404">
-        <v>110070217940</v>
+        <v>110070553101</v>
       </c>
     </row>
     <row r="405">
@@ -3595,7 +3595,7 @@
         <v>404</v>
       </c>
       <c r="B405">
-        <v>110068059406</v>
+        <v>110018446859</v>
       </c>
     </row>
     <row r="406">
@@ -3603,7 +3603,7 @@
         <v>405</v>
       </c>
       <c r="B406">
-        <v>110033194503</v>
+        <v>110055697287</v>
       </c>
     </row>
     <row r="407">
@@ -3611,7 +3611,7 @@
         <v>406</v>
       </c>
       <c r="B407">
-        <v>110005515353</v>
+        <v>110046487958</v>
       </c>
     </row>
     <row r="408">
@@ -3619,7 +3619,7 @@
         <v>407</v>
       </c>
       <c r="B408">
-        <v>110045208896</v>
+        <v>110070473710</v>
       </c>
     </row>
     <row r="409">
@@ -3627,7 +3627,7 @@
         <v>408</v>
       </c>
       <c r="B409">
-        <v>110070056581</v>
+        <v>110006651649</v>
       </c>
     </row>
     <row r="410">
@@ -3635,7 +3635,7 @@
         <v>409</v>
       </c>
       <c r="B410">
-        <v>110071363005</v>
+        <v>110051732559</v>
       </c>
     </row>
     <row r="411">
@@ -3643,7 +3643,7 @@
         <v>410</v>
       </c>
       <c r="B411">
-        <v>110057185941</v>
+        <v>110017568087</v>
       </c>
     </row>
     <row r="412">
@@ -3651,7 +3651,7 @@
         <v>411</v>
       </c>
       <c r="B412">
-        <v>110068527277</v>
+        <v>110071273526</v>
       </c>
     </row>
     <row r="413">
@@ -3659,7 +3659,7 @@
         <v>412</v>
       </c>
       <c r="B413">
-        <v>110020774296</v>
+        <v>110034428206</v>
       </c>
     </row>
     <row r="414">
@@ -3667,7 +3667,7 @@
         <v>413</v>
       </c>
       <c r="B414">
-        <v>110044799368</v>
+        <v>110060004944</v>
       </c>
     </row>
     <row r="415">
@@ -3675,7 +3675,7 @@
         <v>414</v>
       </c>
       <c r="B415">
-        <v>110058742883</v>
+        <v>110065373919</v>
       </c>
     </row>
     <row r="416">
@@ -3683,7 +3683,7 @@
         <v>415</v>
       </c>
       <c r="B416">
-        <v>110070700045</v>
+        <v>110031945162</v>
       </c>
     </row>
     <row r="417">
@@ -3691,7 +3691,7 @@
         <v>416</v>
       </c>
       <c r="B417">
-        <v>110008551487</v>
+        <v>110056240624</v>
       </c>
     </row>
     <row r="418">
@@ -3699,7 +3699,7 @@
         <v>417</v>
       </c>
       <c r="B418">
-        <v>110006389862</v>
+        <v>110040243625</v>
       </c>
     </row>
     <row r="419">
@@ -3707,7 +3707,7 @@
         <v>418</v>
       </c>
       <c r="B419">
-        <v>110071401847</v>
+        <v>110070705665</v>
       </c>
     </row>
     <row r="420">
@@ -3715,7 +3715,7 @@
         <v>419</v>
       </c>
       <c r="B420">
-        <v>110069074913</v>
+        <v>110028173786</v>
       </c>
     </row>
     <row r="421">
@@ -3723,7 +3723,7 @@
         <v>420</v>
       </c>
       <c r="B421">
-        <v>110069182217</v>
+        <v>110032403307</v>
       </c>
     </row>
     <row r="422">
@@ -3731,7 +3731,7 @@
         <v>421</v>
       </c>
       <c r="B422">
-        <v>110031625365</v>
+        <v>110001075504</v>
       </c>
     </row>
     <row r="423">
@@ -3739,7 +3739,7 @@
         <v>422</v>
       </c>
       <c r="B423">
-        <v>110070039924</v>
+        <v>110070208955</v>
       </c>
     </row>
     <row r="424">
@@ -3747,7 +3747,7 @@
         <v>423</v>
       </c>
       <c r="B424">
-        <v>110033998379</v>
+        <v>110038984837</v>
       </c>
     </row>
     <row r="425">
@@ -3755,7 +3755,7 @@
         <v>424</v>
       </c>
       <c r="B425">
-        <v>110069999116</v>
+        <v>110029976612</v>
       </c>
     </row>
     <row r="426">
@@ -3763,7 +3763,7 @@
         <v>425</v>
       </c>
       <c r="B426">
-        <v>110037606436</v>
+        <v>110024997244</v>
       </c>
     </row>
     <row r="427">
@@ -3771,7 +3771,7 @@
         <v>426</v>
       </c>
       <c r="B427">
-        <v>110004691192</v>
+        <v>110070213142</v>
       </c>
     </row>
     <row r="428">
@@ -3779,7 +3779,7 @@
         <v>427</v>
       </c>
       <c r="B428">
-        <v>110070620475</v>
+        <v>110068099881</v>
       </c>
     </row>
     <row r="429">
@@ -3787,7 +3787,7 @@
         <v>428</v>
       </c>
       <c r="B429">
-        <v>110059853706</v>
+        <v>110033244781</v>
       </c>
     </row>
     <row r="430">
@@ -3795,7 +3795,7 @@
         <v>429</v>
       </c>
       <c r="B430">
-        <v>110070524114</v>
+        <v>110005729033</v>
       </c>
     </row>
     <row r="431">
@@ -3803,7 +3803,7 @@
         <v>430</v>
       </c>
       <c r="B431">
-        <v>110070641969</v>
+        <v>110045368794</v>
       </c>
     </row>
     <row r="432">
@@ -3811,7 +3811,7 @@
         <v>431</v>
       </c>
       <c r="B432">
-        <v>110041362799</v>
+        <v>110070041853</v>
       </c>
     </row>
     <row r="433">
@@ -3819,7 +3819,7 @@
         <v>432</v>
       </c>
       <c r="B433">
-        <v>110070426439</v>
+        <v>110071495739</v>
       </c>
     </row>
     <row r="434">
@@ -3827,7 +3827,7 @@
         <v>433</v>
       </c>
       <c r="B434">
-        <v>110003368294</v>
+        <v>110058342388</v>
       </c>
     </row>
     <row r="435">
@@ -3835,7 +3835,7 @@
         <v>434</v>
       </c>
       <c r="B435">
-        <v>110070618368</v>
+        <v>110068530762</v>
       </c>
     </row>
     <row r="436">
@@ -3843,7 +3843,7 @@
         <v>435</v>
       </c>
       <c r="B436">
-        <v>110070061408</v>
+        <v>110072131438</v>
       </c>
     </row>
     <row r="437">
@@ -3851,7 +3851,7 @@
         <v>436</v>
       </c>
       <c r="B437">
-        <v>110007820028</v>
+        <v>110020896707</v>
       </c>
     </row>
     <row r="438">
@@ -3859,7 +3859,7 @@
         <v>437</v>
       </c>
       <c r="B438">
-        <v>110046586716</v>
+        <v>110045032790</v>
       </c>
     </row>
     <row r="439">
@@ -3867,7 +3867,7 @@
         <v>438</v>
       </c>
       <c r="B439">
-        <v>110070712269</v>
+        <v>110059656224</v>
       </c>
     </row>
     <row r="440">
@@ -3875,7 +3875,7 @@
         <v>439</v>
       </c>
       <c r="B440">
-        <v>110041456652</v>
+        <v>110070881312</v>
       </c>
     </row>
     <row r="441">
@@ -3883,7 +3883,7 @@
         <v>440</v>
       </c>
       <c r="B441">
-        <v>110070333110</v>
+        <v>110009007234</v>
       </c>
     </row>
     <row r="442">
@@ -3891,7 +3891,7 @@
         <v>441</v>
       </c>
       <c r="B442">
-        <v>110019149321</v>
+        <v>110006555414</v>
       </c>
     </row>
     <row r="443">
@@ -3899,7 +3899,7 @@
         <v>442</v>
       </c>
       <c r="B443">
-        <v>110065234044</v>
+        <v>110071524321</v>
       </c>
     </row>
     <row r="444">
@@ -3907,7 +3907,7 @@
         <v>443</v>
       </c>
       <c r="B444">
-        <v>110070598942</v>
+        <v>110069033655</v>
       </c>
     </row>
     <row r="445">
@@ -3915,7 +3915,7 @@
         <v>444</v>
       </c>
       <c r="B445">
-        <v>110068280363</v>
+        <v>110069140389</v>
       </c>
     </row>
     <row r="446">
@@ -3923,7 +3923,7 @@
         <v>445</v>
       </c>
       <c r="B446">
-        <v>110071082562</v>
+        <v>110031648536</v>
       </c>
     </row>
     <row r="447">
@@ -3931,7 +3931,7 @@
         <v>446</v>
       </c>
       <c r="B447">
-        <v>110070451096</v>
+        <v>110070023599</v>
       </c>
     </row>
     <row r="448">
@@ -3939,7 +3939,7 @@
         <v>447</v>
       </c>
       <c r="B448">
-        <v>110057066678</v>
+        <v>110034051488</v>
       </c>
     </row>
     <row r="449">
@@ -3947,7 +3947,7 @@
         <v>448</v>
       </c>
       <c r="B449">
-        <v>110070600338</v>
+        <v>110069647216</v>
       </c>
     </row>
     <row r="450">
@@ -3955,7 +3955,7 @@
         <v>449</v>
       </c>
       <c r="B450">
-        <v>110070445699</v>
+        <v>110037772684</v>
       </c>
     </row>
     <row r="451">
@@ -3963,7 +3963,7 @@
         <v>450</v>
       </c>
       <c r="B451">
-        <v>110069048480</v>
+        <v>110004812169</v>
       </c>
     </row>
     <row r="452">
@@ -3971,7 +3971,7 @@
         <v>451</v>
       </c>
       <c r="B452">
-        <v>110070408205</v>
+        <v>110070716061</v>
       </c>
     </row>
     <row r="453">
@@ -3979,7 +3979,7 @@
         <v>452</v>
       </c>
       <c r="B453">
-        <v>110045148988</v>
+        <v>110060260587</v>
       </c>
     </row>
     <row r="454">
@@ -3987,7 +3987,7 @@
         <v>453</v>
       </c>
       <c r="B454">
-        <v>110068775542</v>
+        <v>110070564499</v>
       </c>
     </row>
     <row r="455">
@@ -3995,7 +3995,7 @@
         <v>454</v>
       </c>
       <c r="B455">
-        <v>110013086418</v>
+        <v>110070795085</v>
       </c>
     </row>
     <row r="456">
@@ -4003,7 +4003,7 @@
         <v>455</v>
       </c>
       <c r="B456">
-        <v>110062861540</v>
+        <v>110041480769</v>
       </c>
     </row>
     <row r="457">
@@ -4011,7 +4011,7 @@
         <v>456</v>
       </c>
       <c r="B457">
-        <v>110034050069</v>
+        <v>110070435621</v>
       </c>
     </row>
     <row r="458">
@@ -4019,7 +4019,7 @@
         <v>457</v>
       </c>
       <c r="B458">
-        <v>110009889077</v>
+        <v>110003418917</v>
       </c>
     </row>
     <row r="459">
@@ -4027,7 +4027,7 @@
         <v>458</v>
       </c>
       <c r="B459">
-        <v>110070243087</v>
+        <v>110070712859</v>
       </c>
     </row>
     <row r="460">
@@ -4035,7 +4035,7 @@
         <v>459</v>
       </c>
       <c r="B460">
-        <v>110017542649</v>
+        <v>110070046374</v>
       </c>
     </row>
     <row r="461">
@@ -4043,7 +4043,7 @@
         <v>460</v>
       </c>
       <c r="B461">
-        <v>110040929804</v>
+        <v>110008280984</v>
       </c>
     </row>
     <row r="462">
@@ -4051,7 +4051,7 @@
         <v>461</v>
       </c>
       <c r="B462">
-        <v>110071469844</v>
+        <v>110053879255</v>
       </c>
     </row>
     <row r="463">
@@ -4059,7 +4059,7 @@
         <v>462</v>
       </c>
       <c r="B463">
-        <v>110070371919</v>
+        <v>110070921129</v>
       </c>
     </row>
     <row r="464">
@@ -4067,7 +4067,7 @@
         <v>463</v>
       </c>
       <c r="B464">
-        <v>110071141651</v>
+        <v>110041574034</v>
       </c>
     </row>
     <row r="465">
@@ -4075,7 +4075,7 @@
         <v>464</v>
       </c>
       <c r="B465">
-        <v>110064943897</v>
+        <v>110070333521</v>
       </c>
     </row>
     <row r="466">
@@ -4083,7 +4083,7 @@
         <v>465</v>
       </c>
       <c r="B466">
-        <v>110070838344</v>
+        <v>110019233024</v>
       </c>
     </row>
     <row r="467">
@@ -4091,7 +4091,7 @@
         <v>466</v>
       </c>
       <c r="B467">
-        <v>110058291147</v>
+        <v>110065292427</v>
       </c>
     </row>
     <row r="468">
@@ -4099,7 +4099,7 @@
         <v>467</v>
       </c>
       <c r="B468">
-        <v>110067037003</v>
+        <v>110070692527</v>
       </c>
     </row>
     <row r="469">
@@ -4107,7 +4107,7 @@
         <v>468</v>
       </c>
       <c r="B469">
-        <v>110020073506</v>
+        <v>110068301518</v>
       </c>
     </row>
     <row r="470">
@@ -4115,7 +4115,7 @@
         <v>469</v>
       </c>
       <c r="B470">
-        <v>110064092217</v>
+        <v>110071237842</v>
       </c>
     </row>
     <row r="471">
@@ -4123,7 +4123,7 @@
         <v>470</v>
       </c>
       <c r="B471">
-        <v>110071670196</v>
+        <v>110070464548</v>
       </c>
     </row>
     <row r="472">
@@ -4131,7 +4131,7 @@
         <v>471</v>
       </c>
       <c r="B472">
-        <v>110040430806</v>
+        <v>110058242619</v>
       </c>
     </row>
     <row r="473">
@@ -4139,7 +4139,7 @@
         <v>472</v>
       </c>
       <c r="B473">
-        <v>110000916607</v>
+        <v>110070694912</v>
       </c>
     </row>
     <row r="474">
@@ -4147,7 +4147,7 @@
         <v>473</v>
       </c>
       <c r="B474">
-        <v>110058229439</v>
+        <v>110070456889</v>
       </c>
     </row>
     <row r="475">
@@ -4155,7 +4155,7 @@
         <v>474</v>
       </c>
       <c r="B475">
-        <v>110071504378</v>
+        <v>110069008040</v>
       </c>
     </row>
     <row r="476">
@@ -4163,7 +4163,7 @@
         <v>475</v>
       </c>
       <c r="B476">
-        <v>110024850598</v>
+        <v>110070414297</v>
       </c>
     </row>
     <row r="477">
@@ -4171,7 +4171,7 @@
         <v>476</v>
       </c>
       <c r="B477">
-        <v>110056071254</v>
+        <v>110045289807</v>
       </c>
     </row>
     <row r="478">
@@ -4179,7 +4179,7 @@
         <v>477</v>
       </c>
       <c r="B478">
-        <v>110010039751</v>
+        <v>110068762627</v>
       </c>
     </row>
     <row r="479">
@@ -4187,7 +4187,7 @@
         <v>478</v>
       </c>
       <c r="B479">
-        <v>110070277596</v>
+        <v>110013428754</v>
       </c>
     </row>
     <row r="480">
@@ -4195,7 +4195,7 @@
         <v>479</v>
       </c>
       <c r="B480">
-        <v>110070592333</v>
+        <v>110063229750</v>
       </c>
     </row>
     <row r="481">
@@ -4203,7 +4203,7 @@
         <v>480</v>
       </c>
       <c r="B481">
-        <v>110068165960</v>
+        <v>110034111725</v>
       </c>
     </row>
     <row r="482">
@@ -4211,7 +4211,7 @@
         <v>481</v>
       </c>
       <c r="B482">
-        <v>110009635181</v>
+        <v>110010481950</v>
       </c>
     </row>
     <row r="483">
@@ -4219,7 +4219,7 @@
         <v>482</v>
       </c>
       <c r="B483">
-        <v>110064011233</v>
+        <v>110070240041</v>
       </c>
     </row>
     <row r="484">
@@ -4227,7 +4227,7 @@
         <v>483</v>
       </c>
       <c r="B484">
-        <v>110039245322</v>
+        <v>110017705143</v>
       </c>
     </row>
     <row r="485">
@@ -4235,7 +4235,7 @@
         <v>484</v>
       </c>
       <c r="B485">
-        <v>110005015553</v>
+        <v>110041299804</v>
       </c>
     </row>
     <row r="486">
@@ -4243,7 +4243,7 @@
         <v>485</v>
       </c>
       <c r="B486">
-        <v>110071407616</v>
+        <v>110071670150</v>
       </c>
     </row>
     <row r="487">
@@ -4251,7 +4251,7 @@
         <v>486</v>
       </c>
       <c r="B487">
-        <v>110044249676</v>
+        <v>110070373484</v>
       </c>
     </row>
     <row r="488">
@@ -4259,7 +4259,7 @@
         <v>487</v>
       </c>
       <c r="B488">
-        <v>110019030591</v>
+        <v>110071291493</v>
       </c>
     </row>
     <row r="489">
@@ -4267,7 +4267,7 @@
         <v>488</v>
       </c>
       <c r="B489">
-        <v>110070395926</v>
+        <v>110065002286</v>
       </c>
     </row>
     <row r="490">
@@ -4275,7 +4275,7 @@
         <v>489</v>
       </c>
       <c r="B490">
-        <v>110070547611</v>
+        <v>110071076810</v>
       </c>
     </row>
     <row r="491">
@@ -4283,7 +4283,7 @@
         <v>490</v>
       </c>
       <c r="B491">
-        <v>110017284865</v>
+        <v>110058442797</v>
       </c>
     </row>
     <row r="492">
@@ -4291,7 +4291,7 @@
         <v>491</v>
       </c>
       <c r="B492">
-        <v>110068296686</v>
+        <v>110067218861</v>
       </c>
     </row>
     <row r="493">
@@ -4299,7 +4299,7 @@
         <v>492</v>
       </c>
       <c r="B493">
-        <v>110070598628</v>
+        <v>110020499824</v>
       </c>
     </row>
     <row r="494">
@@ -4307,7 +4307,7 @@
         <v>493</v>
       </c>
       <c r="B494">
-        <v>110070862612</v>
+        <v>110064210580</v>
       </c>
     </row>
     <row r="495">
@@ -4315,7 +4315,7 @@
         <v>494</v>
       </c>
       <c r="B495">
-        <v>110012173824</v>
+        <v>110071804628</v>
       </c>
     </row>
     <row r="496">
@@ -4323,7 +4323,7 @@
         <v>495</v>
       </c>
       <c r="B496">
-        <v>110070205772</v>
+        <v>110040684168</v>
       </c>
     </row>
     <row r="497">
@@ -4331,7 +4331,7 @@
         <v>496</v>
       </c>
       <c r="B497">
-        <v>110006601855</v>
+        <v>110000800054</v>
       </c>
     </row>
     <row r="498">
@@ -4339,7 +4339,7 @@
         <v>497</v>
       </c>
       <c r="B498">
-        <v>110070333549</v>
+        <v>110058378642</v>
       </c>
     </row>
     <row r="499">
@@ -4347,7 +4347,7 @@
         <v>498</v>
       </c>
       <c r="B499">
-        <v>110070698764</v>
+        <v>110071703006</v>
       </c>
     </row>
     <row r="500">
@@ -4355,7 +4355,7 @@
         <v>499</v>
       </c>
       <c r="B500">
-        <v>110037205128</v>
+        <v>110024890867</v>
       </c>
     </row>
     <row r="501">
@@ -4363,7 +4363,7 @@
         <v>500</v>
       </c>
       <c r="B501">
-        <v>110003487502</v>
+        <v>110056195433</v>
       </c>
     </row>
     <row r="502">
@@ -4371,7 +4371,7 @@
         <v>501</v>
       </c>
       <c r="B502">
-        <v>110040597146</v>
+        <v>110010622488</v>
       </c>
     </row>
     <row r="503">
@@ -4379,7 +4379,7 @@
         <v>502</v>
       </c>
       <c r="B503">
-        <v>110022783549</v>
+        <v>110070277823</v>
       </c>
     </row>
     <row r="504">
@@ -4387,7 +4387,7 @@
         <v>503</v>
       </c>
       <c r="B504">
-        <v>110070348944</v>
+        <v>110070684043</v>
       </c>
     </row>
     <row r="505">
@@ -4395,7 +4395,7 @@
         <v>504</v>
       </c>
       <c r="B505">
-        <v>110017018966</v>
+        <v>110068199844</v>
       </c>
     </row>
     <row r="506">
@@ -4403,7 +4403,7 @@
         <v>505</v>
       </c>
       <c r="B506">
-        <v>110044595435</v>
+        <v>110009933144</v>
       </c>
     </row>
     <row r="507">
@@ -4411,7 +4411,7 @@
         <v>506</v>
       </c>
       <c r="B507">
-        <v>110071439079</v>
+        <v>110064143920</v>
       </c>
     </row>
     <row r="508">
@@ -4419,7 +4419,7 @@
         <v>507</v>
       </c>
       <c r="B508">
-        <v>110070700747</v>
+        <v>110039329116</v>
       </c>
     </row>
     <row r="509">
@@ -4427,7 +4427,7 @@
         <v>508</v>
       </c>
       <c r="B509">
-        <v>110020937557</v>
+        <v>110005265300</v>
       </c>
     </row>
     <row r="510">
@@ -4435,7 +4435,7 @@
         <v>509</v>
       </c>
       <c r="B510">
-        <v>110070331199</v>
+        <v>110071531589</v>
       </c>
     </row>
     <row r="511">
@@ -4443,7 +4443,7 @@
         <v>510</v>
       </c>
       <c r="B511">
-        <v>110006256737</v>
+        <v>110044474556</v>
       </c>
     </row>
     <row r="512">
@@ -4451,7 +4451,7 @@
         <v>511</v>
       </c>
       <c r="B512">
-        <v>110008205129</v>
+        <v>110019113252</v>
       </c>
     </row>
     <row r="513">
@@ -4459,7 +4459,7 @@
         <v>512</v>
       </c>
       <c r="B513">
-        <v>110015464843</v>
+        <v>110070397897</v>
       </c>
     </row>
     <row r="514">
@@ -4467,7 +4467,7 @@
         <v>513</v>
       </c>
       <c r="B514">
-        <v>110055839776</v>
+        <v>110070592663</v>
       </c>
     </row>
     <row r="515">
@@ -4475,7 +4475,7 @@
         <v>514</v>
       </c>
       <c r="B515">
-        <v>110018043124</v>
+        <v>110017474785</v>
       </c>
     </row>
     <row r="516">
@@ -4483,7 +4483,7 @@
         <v>515</v>
       </c>
       <c r="B516">
-        <v>110046455224</v>
+        <v>110068318564</v>
       </c>
     </row>
     <row r="517">
@@ -4491,7 +4491,7 @@
         <v>516</v>
       </c>
       <c r="B517">
-        <v>110030020983</v>
+        <v>110070692237</v>
       </c>
     </row>
     <row r="518">
@@ -4499,7 +4499,7 @@
         <v>517</v>
       </c>
       <c r="B518">
-        <v>110002801718</v>
+        <v>110071083112</v>
       </c>
     </row>
     <row r="519">
@@ -4507,7 +4507,7 @@
         <v>518</v>
       </c>
       <c r="B519">
-        <v>110065274143</v>
+        <v>110012548859</v>
       </c>
     </row>
     <row r="520">
@@ -4515,7 +4515,7 @@
         <v>519</v>
       </c>
       <c r="B520">
-        <v>110070228467</v>
+        <v>110070194232</v>
       </c>
     </row>
     <row r="521">
@@ -4523,7 +4523,7 @@
         <v>520</v>
       </c>
       <c r="B521">
-        <v>110070824026</v>
+        <v>110006762066</v>
       </c>
     </row>
     <row r="522">
@@ -4531,7 +4531,7 @@
         <v>521</v>
       </c>
       <c r="B522">
-        <v>110032229906</v>
+        <v>110070333942</v>
       </c>
     </row>
     <row r="523">
@@ -4539,7 +4539,7 @@
         <v>522</v>
       </c>
       <c r="B523">
-        <v>110070551145</v>
+        <v>110070875164</v>
       </c>
     </row>
     <row r="524">
@@ -4547,7 +4547,7 @@
         <v>523</v>
       </c>
       <c r="B524">
-        <v>110040777166</v>
+        <v>110037353994</v>
       </c>
     </row>
     <row r="525">
@@ -4555,7 +4555,7 @@
         <v>524</v>
       </c>
       <c r="B525">
-        <v>110042097254</v>
+        <v>110003533285</v>
       </c>
     </row>
     <row r="526">
@@ -4563,7 +4563,7 @@
         <v>525</v>
       </c>
       <c r="B526">
-        <v>110071077966</v>
+        <v>110040783569</v>
       </c>
     </row>
     <row r="527">
@@ -4571,7 +4571,7 @@
         <v>526</v>
       </c>
       <c r="B527">
-        <v>110070864576</v>
+        <v>110022850654</v>
       </c>
     </row>
     <row r="528">
@@ -4579,7 +4579,7 @@
         <v>527</v>
       </c>
       <c r="B528">
-        <v>110068799946</v>
+        <v>110070349387</v>
       </c>
     </row>
     <row r="529">
@@ -4587,7 +4587,7 @@
         <v>528</v>
       </c>
       <c r="B529">
-        <v>110019278235</v>
+        <v>110017155184</v>
       </c>
     </row>
     <row r="530">
@@ -4595,7 +4595,7 @@
         <v>529</v>
       </c>
       <c r="B530">
-        <v>110015766330</v>
+        <v>110044778283</v>
       </c>
     </row>
     <row r="531">
@@ -4603,7 +4603,7 @@
         <v>530</v>
       </c>
       <c r="B531">
-        <v>110003824390</v>
+        <v>110071656576</v>
       </c>
     </row>
     <row r="532">
@@ -4611,7 +4611,7 @@
         <v>531</v>
       </c>
       <c r="B532">
-        <v>110065600086</v>
+        <v>110070883424</v>
       </c>
     </row>
     <row r="533">
@@ -4619,7 +4619,7 @@
         <v>532</v>
       </c>
       <c r="B533">
-        <v>110070801689</v>
+        <v>110020988181</v>
       </c>
     </row>
     <row r="534">
@@ -4627,7 +4627,7 @@
         <v>533</v>
       </c>
       <c r="B534">
-        <v>110002858471</v>
+        <v>110070331588</v>
       </c>
     </row>
     <row r="535">
@@ -4635,7 +4635,7 @@
         <v>534</v>
       </c>
       <c r="B535">
-        <v>110042128444</v>
+        <v>110006335153</v>
       </c>
     </row>
     <row r="536">
@@ -4643,7 +4643,7 @@
         <v>535</v>
       </c>
       <c r="B536">
-        <v>110035390920</v>
+        <v>110008512868</v>
       </c>
     </row>
     <row r="537">
@@ -4651,7 +4651,7 @@
         <v>536</v>
       </c>
       <c r="B537">
-        <v>110071883778</v>
+        <v>110015543786</v>
       </c>
     </row>
     <row r="538">
@@ -4659,7 +4659,7 @@
         <v>537</v>
       </c>
       <c r="B538">
-        <v>110031908390</v>
+        <v>110055959208</v>
       </c>
     </row>
     <row r="539">
@@ -4667,7 +4667,7 @@
         <v>538</v>
       </c>
       <c r="B539">
-        <v>110058344769</v>
+        <v>110018173714</v>
       </c>
     </row>
     <row r="540">
@@ -4675,7 +4675,7 @@
         <v>539</v>
       </c>
       <c r="B540">
-        <v>110032479271</v>
+        <v>110049478365</v>
       </c>
     </row>
     <row r="541">
@@ -4683,7 +4683,7 @@
         <v>540</v>
       </c>
       <c r="B541">
-        <v>110014172769</v>
+        <v>110030358510</v>
       </c>
     </row>
     <row r="542">
@@ -4691,7 +4691,7 @@
         <v>541</v>
       </c>
       <c r="B542">
-        <v>110070082402</v>
+        <v>110002815847</v>
       </c>
     </row>
     <row r="543">
@@ -4699,7 +4699,7 @@
         <v>542</v>
       </c>
       <c r="B543">
-        <v>110021524705</v>
+        <v>110065336041</v>
       </c>
     </row>
     <row r="544">
@@ -4707,7 +4707,7 @@
         <v>543</v>
       </c>
       <c r="B544">
-        <v>110019178548</v>
+        <v>110070224120</v>
       </c>
     </row>
     <row r="545">
@@ -4715,7 +4715,7 @@
         <v>544</v>
       </c>
       <c r="B545">
-        <v>110032655017</v>
+        <v>110071062039</v>
       </c>
     </row>
     <row r="546">
@@ -4723,7 +4723,7 @@
         <v>545</v>
       </c>
       <c r="B546">
-        <v>110070217866</v>
+        <v>110032251845</v>
       </c>
     </row>
     <row r="547">
@@ -4731,7 +4731,7 @@
         <v>546</v>
       </c>
       <c r="B547">
-        <v>110019394190</v>
+        <v>110070594263</v>
       </c>
     </row>
     <row r="548">
@@ -4739,7 +4739,7 @@
         <v>547</v>
       </c>
       <c r="B548">
-        <v>110006686390</v>
+        <v>110041046855</v>
       </c>
     </row>
     <row r="549">
@@ -4747,7 +4747,7 @@
         <v>548</v>
       </c>
       <c r="B549">
-        <v>110011852566</v>
+        <v>110042310273</v>
       </c>
     </row>
     <row r="550">
@@ -4755,7 +4755,7 @@
         <v>549</v>
       </c>
       <c r="B550">
-        <v>110012611708</v>
+        <v>110071234942</v>
       </c>
     </row>
     <row r="551">
@@ -4763,7 +4763,7 @@
         <v>550</v>
       </c>
       <c r="B551">
-        <v>110019986915</v>
+        <v>110071085838</v>
       </c>
     </row>
     <row r="552">
@@ -4771,7 +4771,7 @@
         <v>551</v>
       </c>
       <c r="B552">
-        <v>110030397835</v>
+        <v>110068786111</v>
       </c>
     </row>
     <row r="553">
@@ -4779,7 +4779,7 @@
         <v>552</v>
       </c>
       <c r="B553">
-        <v>110070819503</v>
+        <v>110019361117</v>
       </c>
     </row>
     <row r="554">
@@ -4787,7 +4787,7 @@
         <v>553</v>
       </c>
       <c r="B554">
-        <v>110056134892</v>
+        <v>110015983676</v>
       </c>
     </row>
     <row r="555">
@@ -4795,7 +4795,7 @@
         <v>554</v>
       </c>
       <c r="B555">
-        <v>110014149377</v>
+        <v>110003891236</v>
       </c>
     </row>
     <row r="556">
@@ -4803,7 +4803,7 @@
         <v>555</v>
       </c>
       <c r="B556">
-        <v>110002897152</v>
+        <v>110072129477</v>
       </c>
     </row>
     <row r="557">
@@ -4811,7 +4811,7 @@
         <v>556</v>
       </c>
       <c r="B557">
-        <v>110071780183</v>
+        <v>110065656828</v>
       </c>
     </row>
     <row r="558">
@@ -4819,7 +4819,7 @@
         <v>557</v>
       </c>
       <c r="B558">
-        <v>110071511594</v>
+        <v>110071018091</v>
       </c>
     </row>
     <row r="559">
@@ -4827,7 +4827,7 @@
         <v>558</v>
       </c>
       <c r="B559">
-        <v>110043317381</v>
+        <v>110002872650</v>
       </c>
     </row>
     <row r="560">
@@ -4835,7 +4835,7 @@
         <v>559</v>
       </c>
       <c r="B560">
-        <v>110032521992</v>
+        <v>110042355386</v>
       </c>
     </row>
     <row r="561">
@@ -4843,7 +4843,7 @@
         <v>560</v>
       </c>
       <c r="B561">
-        <v>110020047171</v>
+        <v>110035464182</v>
       </c>
     </row>
     <row r="562">
@@ -4851,7 +4851,7 @@
         <v>561</v>
       </c>
       <c r="B562">
-        <v>110070353725</v>
+        <v>110071941372</v>
       </c>
     </row>
     <row r="563">
@@ -4859,7 +4859,7 @@
         <v>562</v>
       </c>
       <c r="B563">
-        <v>110015901773</v>
+        <v>110031930891</v>
       </c>
     </row>
     <row r="564">
@@ -4867,7 +4867,7 @@
         <v>563</v>
       </c>
       <c r="B564">
-        <v>110001048376</v>
+        <v>110058512097</v>
       </c>
     </row>
     <row r="565">
@@ -4875,7 +4875,7 @@
         <v>564</v>
       </c>
       <c r="B565">
-        <v>110045458054</v>
+        <v>110032501022</v>
       </c>
     </row>
     <row r="566">
@@ -4883,7 +4883,7 @@
         <v>565</v>
       </c>
       <c r="B566">
-        <v>110018643707</v>
+        <v>110014248091</v>
       </c>
     </row>
     <row r="567">
@@ -4891,7 +4891,7 @@
         <v>566</v>
       </c>
       <c r="B567">
-        <v>110019616254</v>
+        <v>110070061653</v>
       </c>
     </row>
     <row r="568">
@@ -4899,7 +4899,7 @@
         <v>567</v>
       </c>
       <c r="B568">
-        <v>110070280168</v>
+        <v>110021883425</v>
       </c>
     </row>
     <row r="569">
@@ -4907,7 +4907,7 @@
         <v>568</v>
       </c>
       <c r="B569">
-        <v>110005394019</v>
+        <v>110019261984</v>
       </c>
     </row>
     <row r="570">
@@ -4915,7 +4915,7 @@
         <v>569</v>
       </c>
       <c r="B570">
-        <v>110041445424</v>
+        <v>110032820883</v>
       </c>
     </row>
     <row r="571">
@@ -4923,7 +4923,7 @@
         <v>570</v>
       </c>
       <c r="B571">
-        <v>110065892369</v>
+        <v>110070213023</v>
       </c>
     </row>
     <row r="572">
@@ -4931,7 +4931,7 @@
         <v>571</v>
       </c>
       <c r="B572">
-        <v>110068914143</v>
+        <v>110019476985</v>
       </c>
     </row>
     <row r="573">
@@ -4939,7 +4939,7 @@
         <v>572</v>
       </c>
       <c r="B573">
-        <v>110004253138</v>
+        <v>110007013604</v>
       </c>
     </row>
     <row r="574">
@@ -4947,7 +4947,7 @@
         <v>573</v>
       </c>
       <c r="B574">
-        <v>110002792274</v>
+        <v>110012010849</v>
       </c>
     </row>
     <row r="575">
@@ -4955,7 +4955,7 @@
         <v>574</v>
       </c>
       <c r="B575">
-        <v>110071062040</v>
+        <v>110013163628</v>
       </c>
     </row>
     <row r="576">
@@ -4963,7 +4963,7 @@
         <v>575</v>
       </c>
       <c r="B576">
-        <v>110065661910</v>
+        <v>110020396677</v>
       </c>
     </row>
     <row r="577">
@@ -4971,7 +4971,7 @@
         <v>576</v>
       </c>
       <c r="B577">
-        <v>110054911501</v>
+        <v>110030422479</v>
       </c>
     </row>
     <row r="578">
@@ -4979,7 +4979,7 @@
         <v>577</v>
       </c>
       <c r="B578">
-        <v>110070092129</v>
+        <v>110071039916</v>
       </c>
     </row>
     <row r="579">
@@ -4987,7 +4987,7 @@
         <v>578</v>
       </c>
       <c r="B579">
-        <v>110054561283</v>
+        <v>110056246673</v>
       </c>
     </row>
     <row r="580">
@@ -4995,7 +4995,7 @@
         <v>579</v>
       </c>
       <c r="B580">
-        <v>110016669997</v>
+        <v>110071974908</v>
       </c>
     </row>
     <row r="581">
@@ -5003,7 +5003,7 @@
         <v>580</v>
       </c>
       <c r="B581">
-        <v>110034610614</v>
+        <v>110071967763</v>
       </c>
     </row>
     <row r="582">
@@ -5011,7 +5011,7 @@
         <v>581</v>
       </c>
       <c r="B582">
-        <v>110030511444</v>
+        <v>110014229815</v>
       </c>
     </row>
     <row r="583">
@@ -5019,7 +5019,7 @@
         <v>582</v>
       </c>
       <c r="B583">
-        <v>110038257908</v>
+        <v>110002912885</v>
       </c>
     </row>
     <row r="584">
@@ -5027,7 +5027,7 @@
         <v>583</v>
       </c>
       <c r="B584">
-        <v>110022523866</v>
+        <v>110072081718</v>
       </c>
     </row>
     <row r="585">
@@ -5035,7 +5035,7 @@
         <v>584</v>
       </c>
       <c r="B585">
-        <v>110071220309</v>
+        <v>110071878377</v>
       </c>
     </row>
     <row r="586">
@@ -5043,7 +5043,7 @@
         <v>585</v>
       </c>
       <c r="B586">
-        <v>110070570364</v>
+        <v>110071718030</v>
       </c>
     </row>
     <row r="587">
@@ -5051,7 +5051,7 @@
         <v>586</v>
       </c>
       <c r="B587">
-        <v>110009698844</v>
+        <v>110043471935</v>
       </c>
     </row>
     <row r="588">
@@ -5059,7 +5059,7 @@
         <v>587</v>
       </c>
       <c r="B588">
-        <v>110057028069</v>
+        <v>110032543647</v>
       </c>
     </row>
     <row r="589">
@@ -5067,7 +5067,7 @@
         <v>588</v>
       </c>
       <c r="B589">
-        <v>110071437453</v>
+        <v>110020485571</v>
       </c>
     </row>
     <row r="590">
@@ -5075,7 +5075,7 @@
         <v>589</v>
       </c>
       <c r="B590">
-        <v>110011730010</v>
+        <v>110070354189</v>
       </c>
     </row>
     <row r="591">
@@ -5083,7 +5083,7 @@
         <v>590</v>
       </c>
       <c r="B591">
-        <v>110020496952</v>
+        <v>110016681820</v>
       </c>
     </row>
     <row r="592">
@@ -5091,7 +5091,7 @@
         <v>591</v>
       </c>
       <c r="B592">
-        <v>110066492619</v>
+        <v>110001020127</v>
       </c>
     </row>
     <row r="593">
@@ -5099,7 +5099,7 @@
         <v>592</v>
       </c>
       <c r="B593">
-        <v>110013538564</v>
+        <v>110072161228</v>
       </c>
     </row>
     <row r="594">
@@ -5107,7 +5107,7 @@
         <v>593</v>
       </c>
       <c r="B594">
-        <v>110035229204</v>
+        <v>110045789054</v>
       </c>
     </row>
     <row r="595">
@@ -5115,7 +5115,7 @@
         <v>594</v>
       </c>
       <c r="B595">
-        <v>110055547305</v>
+        <v>110018758815</v>
       </c>
     </row>
     <row r="596">
@@ -5123,7 +5123,7 @@
         <v>595</v>
       </c>
       <c r="B596">
-        <v>110044486785</v>
+        <v>110019699913</v>
       </c>
     </row>
     <row r="597">
@@ -5131,7 +5131,7 @@
         <v>596</v>
       </c>
       <c r="B597">
-        <v>110000567958</v>
+        <v>110070280389</v>
       </c>
     </row>
     <row r="598">
@@ -5139,7 +5139,7 @@
         <v>597</v>
       </c>
       <c r="B598">
-        <v>110019161244</v>
+        <v>110005511428</v>
       </c>
     </row>
     <row r="599">
@@ -5147,7 +5147,7 @@
         <v>598</v>
       </c>
       <c r="B599">
-        <v>110064373324</v>
+        <v>110041562779</v>
       </c>
     </row>
     <row r="600">
@@ -5155,7 +5155,7 @@
         <v>599</v>
       </c>
       <c r="B600">
-        <v>110070475247</v>
+        <v>110065958315</v>
       </c>
     </row>
     <row r="601">
@@ -5163,7 +5163,7 @@
         <v>600</v>
       </c>
       <c r="B601">
-        <v>110041313003</v>
+        <v>110068891747</v>
       </c>
     </row>
     <row r="602">
@@ -5171,7 +5171,7 @@
         <v>601</v>
       </c>
       <c r="B602">
-        <v>110019649282</v>
+        <v>110004441952</v>
       </c>
     </row>
     <row r="603">
@@ -5179,7 +5179,7 @@
         <v>602</v>
       </c>
       <c r="B603">
-        <v>110031775345</v>
+        <v>110002806036</v>
       </c>
     </row>
     <row r="604">
@@ -5187,7 +5187,7 @@
         <v>603</v>
       </c>
       <c r="B604">
-        <v>110070218406</v>
+        <v>110071204964</v>
       </c>
     </row>
     <row r="605">
@@ -5195,7 +5195,7 @@
         <v>604</v>
       </c>
       <c r="B605">
-        <v>110019502796</v>
+        <v>110065727477</v>
       </c>
     </row>
     <row r="606">
@@ -5203,7 +5203,7 @@
         <v>605</v>
       </c>
       <c r="B606">
-        <v>110070025613</v>
+        <v>110055144277</v>
       </c>
     </row>
     <row r="607">
@@ -5211,7 +5211,7 @@
         <v>606</v>
       </c>
       <c r="B607">
-        <v>110071268653</v>
+        <v>110070074082</v>
       </c>
     </row>
     <row r="608">
@@ -5219,7 +5219,7 @@
         <v>607</v>
       </c>
       <c r="B608">
-        <v>110071425231</v>
+        <v>110054851022</v>
       </c>
     </row>
     <row r="609">
@@ -5227,7 +5227,7 @@
         <v>608</v>
       </c>
       <c r="B609">
-        <v>110066634823</v>
+        <v>110016878137</v>
       </c>
     </row>
     <row r="610">
@@ -5235,7 +5235,7 @@
         <v>609</v>
       </c>
       <c r="B610">
-        <v>110014327166</v>
+        <v>110034663905</v>
       </c>
     </row>
     <row r="611">
@@ -5243,7 +5243,7 @@
         <v>610</v>
       </c>
       <c r="B611">
-        <v>110004934368</v>
+        <v>110030533698</v>
       </c>
     </row>
     <row r="612">
@@ -5251,7 +5251,7 @@
         <v>611</v>
       </c>
       <c r="B612">
-        <v>110065738839</v>
+        <v>110038447124</v>
       </c>
     </row>
     <row r="613">
@@ -5259,7 +5259,7 @@
         <v>612</v>
       </c>
       <c r="B613">
-        <v>110070519259</v>
+        <v>110022667256</v>
       </c>
     </row>
     <row r="614">
@@ -5267,7 +5267,7 @@
         <v>613</v>
       </c>
       <c r="B614">
-        <v>110022418436</v>
+        <v>110071364551</v>
       </c>
     </row>
     <row r="615">
@@ -5275,7 +5275,7 @@
         <v>614</v>
       </c>
       <c r="B615">
-        <v>110066307865</v>
+        <v>110070609571</v>
       </c>
     </row>
     <row r="616">
@@ -5283,7 +5283,7 @@
         <v>615</v>
       </c>
       <c r="B616">
-        <v>110070412401</v>
+        <v>110010120458</v>
       </c>
     </row>
     <row r="617">
@@ -5291,7 +5291,7 @@
         <v>616</v>
       </c>
       <c r="B617">
-        <v>110000610198</v>
+        <v>110057191248</v>
       </c>
     </row>
     <row r="618">
@@ -5299,7 +5299,7 @@
         <v>617</v>
       </c>
       <c r="B618">
-        <v>110031898793</v>
+        <v>110071654504</v>
       </c>
     </row>
     <row r="619">
@@ -5307,7 +5307,7 @@
         <v>618</v>
       </c>
       <c r="B619">
-        <v>110025320828</v>
+        <v>110011929903</v>
       </c>
     </row>
     <row r="620">
@@ -5315,7 +5315,7 @@
         <v>619</v>
       </c>
       <c r="B620">
-        <v>110065346833</v>
+        <v>110020801417</v>
       </c>
     </row>
     <row r="621">
@@ -5323,7 +5323,7 @@
         <v>620</v>
       </c>
       <c r="B621">
-        <v>110044864386</v>
+        <v>110066563114</v>
       </c>
     </row>
     <row r="622">
@@ -5331,7 +5331,7 @@
         <v>621</v>
       </c>
       <c r="B622">
-        <v>110069219027</v>
+        <v>110013779296</v>
       </c>
     </row>
     <row r="623">
@@ -5339,7 +5339,7 @@
         <v>622</v>
       </c>
       <c r="B623">
-        <v>110070866303</v>
+        <v>110035310847</v>
       </c>
     </row>
     <row r="624">
@@ -5347,7 +5347,7 @@
         <v>623</v>
       </c>
       <c r="B624">
-        <v>110015472059</v>
+        <v>110055706115</v>
       </c>
     </row>
     <row r="625">
@@ -5355,7 +5355,7 @@
         <v>624</v>
       </c>
       <c r="B625">
-        <v>110043642797</v>
+        <v>110044668632</v>
       </c>
     </row>
     <row r="626">
@@ -5363,7 +5363,7 @@
         <v>625</v>
       </c>
       <c r="B626">
-        <v>110032457286</v>
+        <v>110000540905</v>
       </c>
     </row>
     <row r="627">
@@ -5371,7 +5371,7 @@
         <v>626</v>
       </c>
       <c r="B627">
-        <v>110006314639</v>
+        <v>110019244968</v>
       </c>
     </row>
     <row r="628">
@@ -5379,7 +5379,7 @@
         <v>627</v>
       </c>
       <c r="B628">
-        <v>110017612742</v>
+        <v>110064463183</v>
       </c>
     </row>
     <row r="629">
@@ -5387,7 +5387,7 @@
         <v>628</v>
       </c>
       <c r="B629">
-        <v>110037720204</v>
+        <v>110070490940</v>
       </c>
     </row>
     <row r="630">
@@ -5395,7 +5395,7 @@
         <v>629</v>
       </c>
       <c r="B630">
-        <v>110024596784</v>
+        <v>110041448332</v>
       </c>
     </row>
     <row r="631">
@@ -5403,7 +5403,7 @@
         <v>630</v>
       </c>
       <c r="B631">
-        <v>110043949458</v>
+        <v>110019732360</v>
       </c>
     </row>
     <row r="632">
@@ -5411,7 +5411,7 @@
         <v>631</v>
       </c>
       <c r="B632">
-        <v>110070345740</v>
+        <v>110031798080</v>
       </c>
     </row>
     <row r="633">
@@ -5419,7 +5419,7 @@
         <v>632</v>
       </c>
       <c r="B633">
-        <v>110034400342</v>
+        <v>110070213546</v>
       </c>
     </row>
     <row r="634">
@@ -5427,7 +5427,7 @@
         <v>633</v>
       </c>
       <c r="B634">
-        <v>110024852088</v>
+        <v>110019585091</v>
       </c>
     </row>
     <row r="635">
@@ -5435,7 +5435,7 @@
         <v>634</v>
       </c>
       <c r="B635">
-        <v>110037988416</v>
+        <v>110070005931</v>
       </c>
     </row>
     <row r="636">
@@ -5443,7 +5443,7 @@
         <v>635</v>
       </c>
       <c r="B636">
-        <v>110031382858</v>
+        <v>110071402841</v>
       </c>
     </row>
     <row r="637">
@@ -5451,7 +5451,7 @@
         <v>636</v>
       </c>
       <c r="B637">
-        <v>110005750106</v>
+        <v>110071982356</v>
       </c>
     </row>
     <row r="638">
@@ -5459,7 +5459,7 @@
         <v>637</v>
       </c>
       <c r="B638">
-        <v>110042116581</v>
+        <v>110071543368</v>
       </c>
     </row>
     <row r="639">
@@ -5467,7 +5467,7 @@
         <v>638</v>
       </c>
       <c r="B639">
-        <v>110031768479</v>
+        <v>110066710090</v>
       </c>
     </row>
     <row r="640">
@@ -5475,7 +5475,7 @@
         <v>639</v>
       </c>
       <c r="B640">
-        <v>110040425448</v>
+        <v>110014731932</v>
       </c>
     </row>
     <row r="641">
@@ -5483,7 +5483,7 @@
         <v>640</v>
       </c>
       <c r="B641">
-        <v>110070820724</v>
+        <v>110005227959</v>
       </c>
     </row>
     <row r="642">
@@ -5491,7 +5491,7 @@
         <v>641</v>
       </c>
       <c r="B642">
-        <v>110009297867</v>
+        <v>110065805114</v>
       </c>
     </row>
     <row r="643">
@@ -5499,7 +5499,7 @@
         <v>642</v>
       </c>
       <c r="B643">
-        <v>110037158063</v>
+        <v>110070554884</v>
       </c>
     </row>
     <row r="644">
@@ -5507,7 +5507,7 @@
         <v>643</v>
       </c>
       <c r="B644">
-        <v>110066656639</v>
+        <v>110022477577</v>
       </c>
     </row>
     <row r="645">
@@ -5515,7 +5515,7 @@
         <v>644</v>
       </c>
       <c r="B645">
-        <v>110067055769</v>
+        <v>110066376193</v>
       </c>
     </row>
     <row r="646">
@@ -5523,7 +5523,7 @@
         <v>645</v>
       </c>
       <c r="B646">
-        <v>110038246822</v>
+        <v>110070418605</v>
       </c>
     </row>
     <row r="647">
@@ -5531,7 +5531,7 @@
         <v>646</v>
       </c>
       <c r="B647">
-        <v>110015941070</v>
+        <v>110000561927</v>
       </c>
     </row>
     <row r="648">
@@ -5539,7 +5539,7 @@
         <v>647</v>
       </c>
       <c r="B648">
-        <v>110070026471</v>
+        <v>110031921268</v>
       </c>
     </row>
     <row r="649">
@@ -5547,7 +5547,7 @@
         <v>648</v>
       </c>
       <c r="B649">
-        <v>110041143697</v>
+        <v>110025372433</v>
       </c>
     </row>
     <row r="650">
@@ -5555,7 +5555,7 @@
         <v>649</v>
       </c>
       <c r="B650">
-        <v>110070236486</v>
+        <v>110065410683</v>
       </c>
     </row>
     <row r="651">
@@ -5563,7 +5563,7 @@
         <v>650</v>
       </c>
       <c r="B651">
-        <v>110046483159</v>
+        <v>110045071729</v>
       </c>
     </row>
     <row r="652">
@@ -5571,7 +5571,7 @@
         <v>651</v>
       </c>
       <c r="B652">
-        <v>110001789002</v>
+        <v>110069156834</v>
       </c>
     </row>
     <row r="653">
@@ -5579,7 +5579,7 @@
         <v>652</v>
       </c>
       <c r="B653">
-        <v>110007536318</v>
+        <v>110071091222</v>
       </c>
     </row>
     <row r="654">
@@ -5587,7 +5587,7 @@
         <v>653</v>
       </c>
       <c r="B654">
-        <v>110066311315</v>
+        <v>110015551570</v>
       </c>
     </row>
     <row r="655">
@@ -5595,7 +5595,7 @@
         <v>654</v>
       </c>
       <c r="B655">
-        <v>110030928423</v>
+        <v>110043912834</v>
       </c>
     </row>
     <row r="656">
@@ -5603,7 +5603,7 @@
         <v>655</v>
       </c>
       <c r="B656">
-        <v>110071863369</v>
+        <v>110032478664</v>
       </c>
     </row>
     <row r="657">
@@ -5611,7 +5611,7 @@
         <v>656</v>
       </c>
       <c r="B657">
-        <v>110064886075</v>
+        <v>110006451641</v>
       </c>
     </row>
     <row r="658">
@@ -5619,7 +5619,7 @@
         <v>657</v>
       </c>
       <c r="B658">
-        <v>110002007275</v>
+        <v>110017945900</v>
       </c>
     </row>
     <row r="659">
@@ -5627,7 +5627,7 @@
         <v>658</v>
       </c>
       <c r="B659">
-        <v>110004950642</v>
+        <v>110037794287</v>
       </c>
     </row>
     <row r="660">
@@ -5635,7 +5635,7 @@
         <v>659</v>
       </c>
       <c r="B660">
-        <v>110041541436</v>
+        <v>110024698763</v>
       </c>
     </row>
     <row r="661">
@@ -5643,7 +5643,7 @@
         <v>660</v>
       </c>
       <c r="B661">
-        <v>110005468822</v>
+        <v>110044188232</v>
       </c>
     </row>
     <row r="662">
@@ -5651,7 +5651,7 @@
         <v>661</v>
       </c>
       <c r="B662">
-        <v>110056394003</v>
+        <v>110070346190</v>
       </c>
     </row>
     <row r="663">
@@ -5659,7 +5659,7 @@
         <v>662</v>
       </c>
       <c r="B663">
-        <v>110030424422</v>
+        <v>110034450582</v>
       </c>
     </row>
     <row r="664">
@@ -5667,7 +5667,7 @@
         <v>663</v>
       </c>
       <c r="B664">
-        <v>110065028295</v>
+        <v>110024919212</v>
       </c>
     </row>
     <row r="665">
@@ -5675,7 +5675,7 @@
         <v>664</v>
       </c>
       <c r="B665">
-        <v>110008850797</v>
+        <v>110038223794</v>
       </c>
     </row>
     <row r="666">
@@ -5683,7 +5683,7 @@
         <v>665</v>
       </c>
       <c r="B666">
-        <v>110063691296</v>
+        <v>110031458161</v>
       </c>
     </row>
     <row r="667">
@@ -5691,7 +5691,7 @@
         <v>666</v>
       </c>
       <c r="B667">
-        <v>110044756118</v>
+        <v>110005942490</v>
       </c>
     </row>
     <row r="668">
@@ -5699,7 +5699,7 @@
         <v>667</v>
       </c>
       <c r="B668">
-        <v>110044676730</v>
+        <v>110042340053</v>
       </c>
     </row>
     <row r="669">
@@ -5707,7 +5707,7 @@
         <v>668</v>
       </c>
       <c r="B669">
-        <v>110058689003</v>
+        <v>110031791185</v>
       </c>
     </row>
     <row r="670">
@@ -5715,7 +5715,7 @@
         <v>669</v>
       </c>
       <c r="B670">
-        <v>110034724350</v>
+        <v>110040678692</v>
       </c>
     </row>
     <row r="671">
@@ -5723,7 +5723,7 @@
         <v>670</v>
       </c>
       <c r="B671">
-        <v>110022688135</v>
+        <v>110071042464</v>
       </c>
     </row>
     <row r="672">
@@ -5731,7 +5731,7 @@
         <v>671</v>
       </c>
       <c r="B672">
-        <v>110070413982</v>
+        <v>110009626173</v>
       </c>
     </row>
     <row r="673">
@@ -5739,7 +5739,7 @@
         <v>672</v>
       </c>
       <c r="B673">
-        <v>110004501600</v>
+        <v>110037307624</v>
       </c>
     </row>
     <row r="674">
@@ -5747,7 +5747,7 @@
         <v>673</v>
       </c>
       <c r="B674">
-        <v>110027306056</v>
+        <v>110066734582</v>
       </c>
     </row>
     <row r="675">
@@ -5755,7 +5755,7 @@
         <v>674</v>
       </c>
       <c r="B675">
-        <v>110070576471</v>
+        <v>110067248295</v>
       </c>
     </row>
     <row r="676">
@@ -5763,7 +5763,7 @@
         <v>675</v>
       </c>
       <c r="B676">
-        <v>110057051283</v>
+        <v>110038431961</v>
       </c>
     </row>
     <row r="677">
@@ -5771,7 +5771,7 @@
         <v>676</v>
       </c>
       <c r="B677">
-        <v>110039395080</v>
+        <v>110016725061</v>
       </c>
     </row>
     <row r="678">
@@ -5779,7 +5779,7 @@
         <v>677</v>
       </c>
       <c r="B678">
-        <v>110058592517</v>
+        <v>110070006876</v>
       </c>
     </row>
     <row r="679">
@@ -5787,7 +5787,7 @@
         <v>678</v>
       </c>
       <c r="B679">
-        <v>110003075528</v>
+        <v>110041391348</v>
       </c>
     </row>
     <row r="680">
@@ -5795,7 +5795,7 @@
         <v>679</v>
       </c>
       <c r="B680">
-        <v>110014108152</v>
+        <v>110070230334</v>
       </c>
     </row>
     <row r="681">
@@ -5803,7 +5803,7 @@
         <v>680</v>
       </c>
       <c r="B681">
-        <v>110068553416</v>
+        <v>110050694717</v>
       </c>
     </row>
     <row r="682">
@@ -5811,7 +5811,7 @@
         <v>681</v>
       </c>
       <c r="B682">
-        <v>110020719775</v>
+        <v>110001795102</v>
       </c>
     </row>
     <row r="683">
@@ -5819,7 +5819,7 @@
         <v>682</v>
       </c>
       <c r="B683">
-        <v>110067019318</v>
+        <v>110008034938</v>
       </c>
     </row>
     <row r="684">
@@ -5827,7 +5827,7 @@
         <v>683</v>
       </c>
       <c r="B684">
-        <v>110025968086</v>
+        <v>110066379617</v>
       </c>
     </row>
     <row r="685">
@@ -5835,7 +5835,7 @@
         <v>684</v>
       </c>
       <c r="B685">
-        <v>110018826467</v>
+        <v>110031282305</v>
       </c>
     </row>
     <row r="686">
@@ -5843,7 +5843,7 @@
         <v>685</v>
       </c>
       <c r="B686">
-        <v>110042763989</v>
+        <v>110071923106</v>
       </c>
     </row>
     <row r="687">
@@ -5851,7 +5851,7 @@
         <v>686</v>
       </c>
       <c r="B687">
-        <v>110071506377</v>
+        <v>110064942969</v>
       </c>
     </row>
     <row r="688">
@@ -5859,7 +5859,7 @@
         <v>687</v>
       </c>
       <c r="B688">
-        <v>110070113304</v>
+        <v>110002023453</v>
       </c>
     </row>
     <row r="689">
@@ -5867,7 +5867,7 @@
         <v>688</v>
       </c>
       <c r="B689">
-        <v>110024535065</v>
+        <v>110005245074</v>
       </c>
     </row>
     <row r="690">
@@ -5875,7 +5875,7 @@
         <v>689</v>
       </c>
       <c r="B690">
-        <v>110056060408</v>
+        <v>110041719021</v>
       </c>
     </row>
     <row r="691">
@@ -5883,7 +5883,7 @@
         <v>690</v>
       </c>
       <c r="B691">
-        <v>110003375339</v>
+        <v>110005637980</v>
       </c>
     </row>
     <row r="692">
@@ -5891,7 +5891,7 @@
         <v>691</v>
       </c>
       <c r="B692">
-        <v>110031370647</v>
+        <v>110057017204</v>
       </c>
     </row>
     <row r="693">
@@ -5899,7 +5899,7 @@
         <v>692</v>
       </c>
       <c r="B693">
-        <v>110043366595</v>
+        <v>110030477482</v>
       </c>
     </row>
     <row r="694">
@@ -5907,7 +5907,7 @@
         <v>693</v>
       </c>
       <c r="B694">
-        <v>110070434644</v>
+        <v>110065083297</v>
       </c>
     </row>
     <row r="695">
@@ -5915,7 +5915,7 @@
         <v>694</v>
       </c>
       <c r="B695">
-        <v>110028095861</v>
+        <v>110009459175</v>
       </c>
     </row>
     <row r="696">
@@ -5923,7 +5923,7 @@
         <v>695</v>
       </c>
       <c r="B696">
-        <v>110070996476</v>
+        <v>110063841106</v>
       </c>
     </row>
     <row r="697">
@@ -5931,7 +5931,7 @@
         <v>696</v>
       </c>
       <c r="B697">
-        <v>110003353371</v>
+        <v>110044981222</v>
       </c>
     </row>
     <row r="698">
@@ -5939,7 +5939,7 @@
         <v>697</v>
       </c>
       <c r="B698">
-        <v>110033460573</v>
+        <v>110044886308</v>
       </c>
     </row>
     <row r="699">
@@ -5947,7 +5947,7 @@
         <v>698</v>
       </c>
       <c r="B699">
-        <v>110013213593</v>
+        <v>110058894594</v>
       </c>
     </row>
     <row r="700">
@@ -5955,7 +5955,7 @@
         <v>699</v>
       </c>
       <c r="B700">
-        <v>110069177553</v>
+        <v>110034793276</v>
       </c>
     </row>
     <row r="701">
@@ -5963,7 +5963,7 @@
         <v>700</v>
       </c>
       <c r="B701">
-        <v>110071163824</v>
+        <v>110022722455</v>
       </c>
     </row>
     <row r="702">
@@ -5971,7 +5971,7 @@
         <v>701</v>
       </c>
       <c r="B702">
-        <v>110033414865</v>
+        <v>110070420294</v>
       </c>
     </row>
     <row r="703">
@@ -5979,7 +5979,7 @@
         <v>702</v>
       </c>
       <c r="B703">
-        <v>110017718781</v>
+        <v>110004664532</v>
       </c>
     </row>
     <row r="704">
@@ -5987,7 +5987,7 @@
         <v>703</v>
       </c>
       <c r="B704">
-        <v>110008444120</v>
+        <v>110027758781</v>
       </c>
     </row>
     <row r="705">
@@ -5995,7 +5995,7 @@
         <v>704</v>
       </c>
       <c r="B705">
-        <v>110034239991</v>
+        <v>110070618443</v>
       </c>
     </row>
     <row r="706">
@@ -6003,7 +6003,7 @@
         <v>705</v>
       </c>
       <c r="B706">
-        <v>110014141482</v>
+        <v>110058226012</v>
       </c>
     </row>
     <row r="707">
@@ -6011,7 +6011,7 @@
         <v>706</v>
       </c>
       <c r="B707">
-        <v>110040066790</v>
+        <v>110039483706</v>
       </c>
     </row>
     <row r="708">
@@ -6019,7 +6019,7 @@
         <v>707</v>
       </c>
       <c r="B708">
-        <v>110019223053</v>
+        <v>110058791455</v>
       </c>
     </row>
     <row r="709">
@@ -6027,7 +6027,7 @@
         <v>708</v>
       </c>
       <c r="B709">
-        <v>110070401844</v>
+        <v>110003115389</v>
       </c>
     </row>
     <row r="710">
@@ -6035,7 +6035,7 @@
         <v>709</v>
       </c>
       <c r="B710">
-        <v>110018415053</v>
+        <v>110014186406</v>
       </c>
     </row>
     <row r="711">
@@ -6043,7 +6043,7 @@
         <v>710</v>
       </c>
       <c r="B711">
-        <v>110066427236</v>
+        <v>110068556075</v>
       </c>
     </row>
     <row r="712">
@@ -6051,7 +6051,7 @@
         <v>711</v>
       </c>
       <c r="B712">
-        <v>110011626277</v>
+        <v>110020877041</v>
       </c>
     </row>
     <row r="713">
@@ -6059,7 +6059,7 @@
         <v>712</v>
       </c>
       <c r="B713">
-        <v>110070702551</v>
+        <v>110067201281</v>
       </c>
     </row>
     <row r="714">
@@ -6067,7 +6067,7 @@
         <v>713</v>
       </c>
       <c r="B714">
-        <v>110071222445</v>
+        <v>110027252005</v>
       </c>
     </row>
     <row r="715">
@@ -6075,7 +6075,7 @@
         <v>714</v>
       </c>
       <c r="B715">
-        <v>110070273246</v>
+        <v>110018990056</v>
       </c>
     </row>
     <row r="716">
@@ -6083,7 +6083,7 @@
         <v>715</v>
       </c>
       <c r="B716">
-        <v>110007037839</v>
+        <v>110043269548</v>
       </c>
     </row>
     <row r="717">
@@ -6091,7 +6091,7 @@
         <v>716</v>
       </c>
       <c r="B717">
-        <v>110029900472</v>
+        <v>110071707540</v>
       </c>
     </row>
     <row r="718">
@@ -6099,7 +6099,7 @@
         <v>717</v>
       </c>
       <c r="B718">
-        <v>110071269835</v>
+        <v>110070097641</v>
       </c>
     </row>
     <row r="719">
@@ -6107,7 +6107,7 @@
         <v>718</v>
       </c>
       <c r="B719">
-        <v>110044550107</v>
+        <v>110024593732</v>
       </c>
     </row>
     <row r="720">
@@ -6115,7 +6115,7 @@
         <v>719</v>
       </c>
       <c r="B720">
-        <v>110037352520</v>
+        <v>110056183909</v>
       </c>
     </row>
     <row r="721">
@@ -6123,7 +6123,7 @@
         <v>720</v>
       </c>
       <c r="B721">
-        <v>110039011253</v>
+        <v>110003425730</v>
       </c>
     </row>
     <row r="722">
@@ -6131,7 +6131,7 @@
         <v>721</v>
       </c>
       <c r="B722">
-        <v>110017121461</v>
+        <v>110031429470</v>
       </c>
     </row>
     <row r="723">
@@ -6139,7 +6139,7 @@
         <v>722</v>
       </c>
       <c r="B723">
-        <v>110014377735</v>
+        <v>110043581380</v>
       </c>
     </row>
     <row r="724">
@@ -6147,7 +6147,7 @@
         <v>723</v>
       </c>
       <c r="B724">
-        <v>110055409801</v>
+        <v>110070445923</v>
       </c>
     </row>
     <row r="725">
@@ -6155,7 +6155,7 @@
         <v>724</v>
       </c>
       <c r="B725">
-        <v>110006808758</v>
+        <v>110028138021</v>
       </c>
     </row>
     <row r="726">
@@ -6163,7 +6163,7 @@
         <v>725</v>
       </c>
       <c r="B726">
-        <v>110031889972</v>
+        <v>110071178375</v>
       </c>
     </row>
     <row r="727">
@@ -6171,7 +6171,7 @@
         <v>726</v>
       </c>
       <c r="B727">
-        <v>110069063925</v>
+        <v>110003378728</v>
       </c>
     </row>
     <row r="728">
@@ -6179,7 +6179,7 @@
         <v>727</v>
       </c>
       <c r="B728">
-        <v>110066442521</v>
+        <v>110033503395</v>
       </c>
     </row>
     <row r="729">
@@ -6187,7 +6187,7 @@
         <v>728</v>
       </c>
       <c r="B729">
-        <v>110055750575</v>
+        <v>110013487066</v>
       </c>
     </row>
     <row r="730">
@@ -6195,7 +6195,7 @@
         <v>729</v>
       </c>
       <c r="B730">
-        <v>110071526347</v>
+        <v>110069138043</v>
       </c>
     </row>
     <row r="731">
@@ -6203,7 +6203,7 @@
         <v>730</v>
       </c>
       <c r="B731">
-        <v>110012192000</v>
+        <v>110071328063</v>
       </c>
     </row>
     <row r="732">
@@ -6211,7 +6211,7 @@
         <v>731</v>
       </c>
       <c r="B732">
-        <v>110070475023</v>
+        <v>110033460779</v>
       </c>
     </row>
     <row r="733">
@@ -6219,7 +6219,7 @@
         <v>732</v>
       </c>
       <c r="B733">
-        <v>110045120640</v>
+        <v>110018043268</v>
       </c>
     </row>
     <row r="734">
@@ -6227,7 +6227,7 @@
         <v>733</v>
       </c>
       <c r="B734">
-        <v>110065052347</v>
+        <v>110008844590</v>
       </c>
     </row>
     <row r="735">
@@ -6235,7 +6235,7 @@
         <v>734</v>
       </c>
       <c r="B735">
-        <v>110071880354</v>
+        <v>110034291950</v>
       </c>
     </row>
     <row r="736">
@@ -6243,7 +6243,7 @@
         <v>735</v>
       </c>
       <c r="B736">
-        <v>110035123158</v>
+        <v>110014221813</v>
       </c>
     </row>
     <row r="737">
@@ -6251,7 +6251,7 @@
         <v>736</v>
       </c>
       <c r="B737">
-        <v>110043008269</v>
+        <v>110040226662</v>
       </c>
     </row>
     <row r="738">
@@ -6259,7 +6259,7 @@
         <v>737</v>
       </c>
       <c r="B738">
-        <v>110060310676</v>
+        <v>110019305777</v>
       </c>
     </row>
     <row r="739">
@@ -6267,7 +6267,7 @@
         <v>738</v>
       </c>
       <c r="B739">
-        <v>110071707825</v>
+        <v>110070407047</v>
       </c>
     </row>
     <row r="740">
@@ -6275,7 +6275,7 @@
         <v>739</v>
       </c>
       <c r="B740">
-        <v>110003557311</v>
+        <v>110072163907</v>
       </c>
     </row>
     <row r="741">
@@ -6283,7 +6283,7 @@
         <v>740</v>
       </c>
       <c r="B741">
-        <v>110070457936</v>
+        <v>110018538019</v>
       </c>
     </row>
     <row r="742">
@@ -6291,7 +6291,7 @@
         <v>741</v>
       </c>
       <c r="B742">
-        <v>110032354155</v>
+        <v>110066496214</v>
       </c>
     </row>
     <row r="743">
@@ -6299,7 +6299,7 @@
         <v>742</v>
       </c>
       <c r="B743">
-        <v>110067950809</v>
+        <v>110071991008</v>
       </c>
     </row>
     <row r="744">
@@ -6307,7 +6307,7 @@
         <v>743</v>
       </c>
       <c r="B744">
-        <v>110070703202</v>
+        <v>110011819050</v>
       </c>
     </row>
     <row r="745">
@@ -6315,7 +6315,7 @@
         <v>744</v>
       </c>
       <c r="B745">
-        <v>110060059680</v>
+        <v>110070892127</v>
       </c>
     </row>
     <row r="746">
@@ -6323,7 +6323,7 @@
         <v>745</v>
       </c>
       <c r="B746">
-        <v>110070422907</v>
+        <v>110071367904</v>
       </c>
     </row>
     <row r="747">
@@ -6331,7 +6331,7 @@
         <v>746</v>
       </c>
       <c r="B747">
-        <v>110033385307</v>
+        <v>110070273457</v>
       </c>
     </row>
     <row r="748">
@@ -6339,7 +6339,7 @@
         <v>747</v>
       </c>
       <c r="B748">
-        <v>110004032895</v>
+        <v>110007398020</v>
       </c>
     </row>
     <row r="749">
@@ -6347,7 +6347,7 @@
         <v>748</v>
       </c>
       <c r="B749">
-        <v>110006232013</v>
+        <v>110029921510</v>
       </c>
     </row>
     <row r="750">
@@ -6355,7 +6355,7 @@
         <v>749</v>
       </c>
       <c r="B750">
-        <v>110017584167</v>
+        <v>110071978927</v>
       </c>
     </row>
     <row r="751">
@@ -6363,7 +6363,7 @@
         <v>750</v>
       </c>
       <c r="B751">
-        <v>110056079648</v>
+        <v>110071404634</v>
       </c>
     </row>
     <row r="752">
@@ -6371,7 +6371,7 @@
         <v>751</v>
       </c>
       <c r="B752">
-        <v>110021291760</v>
+        <v>110072028221</v>
       </c>
     </row>
     <row r="753">
@@ -6379,7 +6379,7 @@
         <v>752</v>
       </c>
       <c r="B753">
-        <v>110071670910</v>
+        <v>110044730280</v>
       </c>
     </row>
     <row r="754">
@@ -6387,7 +6387,7 @@
         <v>753</v>
       </c>
       <c r="B754">
-        <v>110064900969</v>
+        <v>110037571151</v>
       </c>
     </row>
     <row r="755">
@@ -6395,7 +6395,7 @@
         <v>754</v>
       </c>
       <c r="B755">
-        <v>110054288374</v>
+        <v>110039252992</v>
       </c>
     </row>
     <row r="756">
@@ -6403,7 +6403,7 @@
         <v>755</v>
       </c>
       <c r="B756">
-        <v>110044678122</v>
+        <v>110017330235</v>
       </c>
     </row>
     <row r="757">
@@ -6411,7 +6411,7 @@
         <v>756</v>
       </c>
       <c r="B757">
-        <v>110019731316</v>
+        <v>110014854719</v>
       </c>
     </row>
     <row r="758">
@@ -6419,7 +6419,7 @@
         <v>757</v>
       </c>
       <c r="B758">
-        <v>110070466814</v>
+        <v>110055613545</v>
       </c>
     </row>
     <row r="759">
@@ -6427,7 +6427,7 @@
         <v>758</v>
       </c>
       <c r="B759">
-        <v>110068851362</v>
+        <v>110007254675</v>
       </c>
     </row>
     <row r="760">
@@ -6435,7 +6435,7 @@
         <v>759</v>
       </c>
       <c r="B760">
-        <v>110035798928</v>
+        <v>110031912367</v>
       </c>
     </row>
     <row r="761">
@@ -6443,7 +6443,7 @@
         <v>760</v>
       </c>
       <c r="B761">
-        <v>110070209814</v>
+        <v>110069022220</v>
       </c>
     </row>
     <row r="762">
@@ -6451,7 +6451,7 @@
         <v>761</v>
       </c>
       <c r="B762">
-        <v>110069993787</v>
+        <v>110066513053</v>
       </c>
     </row>
     <row r="763">
@@ -6459,7 +6459,7 @@
         <v>762</v>
       </c>
       <c r="B763">
-        <v>110070122744</v>
+        <v>110055854446</v>
       </c>
     </row>
     <row r="764">
@@ -6467,7 +6467,7 @@
         <v>763</v>
       </c>
       <c r="B764">
-        <v>110001553159</v>
+        <v>110071726750</v>
       </c>
     </row>
     <row r="765">
@@ -6475,7 +6475,7 @@
         <v>764</v>
       </c>
       <c r="B765">
-        <v>110017082299</v>
+        <v>110012572037</v>
       </c>
     </row>
     <row r="766">
@@ -6483,7 +6483,7 @@
         <v>765</v>
       </c>
       <c r="B766">
-        <v>110030530904</v>
+        <v>110070490551</v>
       </c>
     </row>
     <row r="767">
@@ -6491,7 +6491,7 @@
         <v>766</v>
       </c>
       <c r="B767">
-        <v>110064406879</v>
+        <v>110045253907</v>
       </c>
     </row>
     <row r="768">
@@ -6499,7 +6499,7 @@
         <v>767</v>
       </c>
       <c r="B768">
-        <v>110070444390</v>
+        <v>110065104586</v>
       </c>
     </row>
     <row r="769">
@@ -6507,7 +6507,7 @@
         <v>768</v>
       </c>
       <c r="B769">
-        <v>110036200526</v>
+        <v>110071934803</v>
       </c>
     </row>
     <row r="770">
@@ -6515,7 +6515,7 @@
         <v>769</v>
       </c>
       <c r="B770">
-        <v>110012929956</v>
+        <v>110035213603</v>
       </c>
     </row>
     <row r="771">
@@ -6523,7 +6523,7 @@
         <v>770</v>
       </c>
       <c r="B771">
-        <v>110045468061</v>
+        <v>110043361475</v>
       </c>
     </row>
     <row r="772">
@@ -6531,7 +6531,7 @@
         <v>771</v>
       </c>
       <c r="B772">
-        <v>110066576244</v>
+        <v>110061909476</v>
       </c>
     </row>
     <row r="773">
@@ -6539,7 +6539,7 @@
         <v>772</v>
       </c>
       <c r="B773">
-        <v>110019768081</v>
+        <v>110071819665</v>
       </c>
     </row>
     <row r="774">
@@ -6547,7 +6547,7 @@
         <v>773</v>
       </c>
       <c r="B774">
-        <v>110070698293</v>
+        <v>110003621554</v>
       </c>
     </row>
     <row r="775">
@@ -6555,7 +6555,7 @@
         <v>774</v>
       </c>
       <c r="B775">
-        <v>110018777153</v>
+        <v>110070472476</v>
       </c>
     </row>
     <row r="776">
@@ -6563,7 +6563,7 @@
         <v>775</v>
       </c>
       <c r="B776">
-        <v>110070011043</v>
+        <v>110032375622</v>
       </c>
     </row>
     <row r="777">
@@ -6571,7 +6571,7 @@
         <v>776</v>
       </c>
       <c r="B777">
-        <v>110044460464</v>
+        <v>110067989403</v>
       </c>
     </row>
     <row r="778">
@@ -6579,7 +6579,7 @@
         <v>777</v>
       </c>
       <c r="B778">
-        <v>110003095445</v>
+        <v>110070894094</v>
       </c>
     </row>
     <row r="779">
@@ -6587,7 +6587,7 @@
         <v>778</v>
       </c>
       <c r="B779">
-        <v>110066824039</v>
+        <v>110060555420</v>
       </c>
     </row>
     <row r="780">
@@ -6595,7 +6595,7 @@
         <v>779</v>
       </c>
       <c r="B780">
-        <v>110015416655</v>
+        <v>110070429668</v>
       </c>
     </row>
     <row r="781">
@@ -6603,7 +6603,7 @@
         <v>780</v>
       </c>
       <c r="B781">
-        <v>110070407164</v>
+        <v>110033436583</v>
       </c>
     </row>
     <row r="782">
@@ -6611,7 +6611,7 @@
         <v>781</v>
       </c>
       <c r="B782">
-        <v>110065275730</v>
+        <v>110004163770</v>
       </c>
     </row>
     <row r="783">
@@ -6619,7 +6619,7 @@
         <v>782</v>
       </c>
       <c r="B783">
-        <v>110003948818</v>
+        <v>110006312837</v>
       </c>
     </row>
     <row r="784">
@@ -6627,7 +6627,7 @@
         <v>783</v>
       </c>
       <c r="B784">
-        <v>110056178522</v>
+        <v>110017829251</v>
       </c>
     </row>
     <row r="785">
@@ -6635,7 +6635,7 @@
         <v>784</v>
       </c>
       <c r="B785">
-        <v>110031996687</v>
+        <v>110056203415</v>
       </c>
     </row>
     <row r="786">
@@ -6643,7 +6643,7 @@
         <v>785</v>
       </c>
       <c r="B786">
-        <v>110070208316</v>
+        <v>110021350321</v>
       </c>
     </row>
     <row r="787">
@@ -6651,7 +6651,7 @@
         <v>786</v>
       </c>
       <c r="B787">
-        <v>110067267157</v>
+        <v>110071806871</v>
       </c>
     </row>
     <row r="788">
@@ -6659,7 +6659,7 @@
         <v>787</v>
       </c>
       <c r="B788">
-        <v>110001376118</v>
+        <v>110064956739</v>
       </c>
     </row>
     <row r="789">
@@ -6667,7 +6667,7 @@
         <v>788</v>
       </c>
       <c r="B789">
-        <v>110071432247</v>
+        <v>110054475769</v>
       </c>
     </row>
     <row r="790">
@@ -6675,7 +6675,7 @@
         <v>789</v>
       </c>
       <c r="B790">
-        <v>110020578631</v>
+        <v>110044890062</v>
       </c>
     </row>
     <row r="791">
@@ -6683,7 +6683,7 @@
         <v>790</v>
       </c>
       <c r="B791">
-        <v>110040777503</v>
+        <v>110019816840</v>
       </c>
     </row>
     <row r="792">
@@ -6691,7 +6691,7 @@
         <v>791</v>
       </c>
       <c r="B792">
-        <v>110066244139</v>
+        <v>110070481739</v>
       </c>
     </row>
     <row r="793">
@@ -6699,7 +6699,7 @@
         <v>792</v>
       </c>
       <c r="B793">
-        <v>110029404491</v>
+        <v>110068832641</v>
       </c>
     </row>
     <row r="794">
@@ -6707,7 +6707,7 @@
         <v>793</v>
       </c>
       <c r="B794">
-        <v>110010884891</v>
+        <v>110036148790</v>
       </c>
     </row>
     <row r="795">
@@ -6715,7 +6715,7 @@
         <v>794</v>
       </c>
       <c r="B795">
-        <v>110070052804</v>
+        <v>110070202936</v>
       </c>
     </row>
     <row r="796">
@@ -6723,7 +6723,7 @@
         <v>795</v>
       </c>
       <c r="B796">
-        <v>110068907080</v>
+        <v>110069594228</v>
       </c>
     </row>
     <row r="797">
@@ -6731,7 +6731,7 @@
         <v>796</v>
       </c>
       <c r="B797">
-        <v>110070064706</v>
+        <v>110070106395</v>
       </c>
     </row>
     <row r="798">
@@ -6739,7 +6739,7 @@
         <v>797</v>
       </c>
       <c r="B798">
-        <v>110020291851</v>
+        <v>110001564904</v>
       </c>
     </row>
     <row r="799">
@@ -6747,7 +6747,7 @@
         <v>798</v>
       </c>
       <c r="B799">
-        <v>110059676765</v>
+        <v>110017293105</v>
       </c>
     </row>
     <row r="800">
@@ -6755,7 +6755,7 @@
         <v>799</v>
       </c>
       <c r="B800">
-        <v>110070792791</v>
+        <v>110030559330</v>
       </c>
     </row>
     <row r="801">
@@ -6763,7 +6763,7 @@
         <v>800</v>
       </c>
       <c r="B801">
-        <v>110044163286</v>
+        <v>110064489860</v>
       </c>
     </row>
     <row r="802">
@@ -6771,7 +6771,7 @@
         <v>801</v>
       </c>
       <c r="B802">
-        <v>110070344166</v>
+        <v>110070455518</v>
       </c>
     </row>
     <row r="803">
@@ -6779,7 +6779,7 @@
         <v>802</v>
       </c>
       <c r="B803">
-        <v>110039251010</v>
+        <v>110036272618</v>
       </c>
     </row>
     <row r="804">
@@ -6787,7 +6787,7 @@
         <v>803</v>
       </c>
       <c r="B804">
-        <v>110070591991</v>
+        <v>110013303433</v>
       </c>
     </row>
     <row r="805">
@@ -6795,7 +6795,7 @@
         <v>804</v>
       </c>
       <c r="B805">
-        <v>110070364439</v>
+        <v>110045799800</v>
       </c>
     </row>
     <row r="806">
@@ -6803,7 +6803,7 @@
         <v>805</v>
       </c>
       <c r="B806">
-        <v>110018406303</v>
+        <v>110066647267</v>
       </c>
     </row>
     <row r="807">
@@ -6811,7 +6811,7 @@
         <v>806</v>
       </c>
       <c r="B807">
-        <v>110035099470</v>
+        <v>110019856681</v>
       </c>
     </row>
     <row r="808">
@@ -6819,7 +6819,7 @@
         <v>807</v>
       </c>
       <c r="B808">
-        <v>110071539298</v>
+        <v>110070874093</v>
       </c>
     </row>
     <row r="809">
@@ -6827,7 +6827,7 @@
         <v>808</v>
       </c>
       <c r="B809">
-        <v>110056068259</v>
+        <v>110018914362</v>
       </c>
     </row>
     <row r="810">
@@ -6835,7 +6835,7 @@
         <v>809</v>
       </c>
       <c r="B810">
-        <v>110034371114</v>
+        <v>110069691961</v>
       </c>
     </row>
     <row r="811">
@@ -6843,7 +6843,7 @@
         <v>810</v>
       </c>
       <c r="B811">
-        <v>110013165216</v>
+        <v>110044647102</v>
       </c>
     </row>
     <row r="812">
@@ -6851,7 +6851,7 @@
         <v>811</v>
       </c>
       <c r="B812">
-        <v>110068524868</v>
+        <v>110003133136</v>
       </c>
     </row>
     <row r="813">
@@ -6859,7 +6859,7 @@
         <v>812</v>
       </c>
       <c r="B813">
-        <v>110041195989</v>
+        <v>110066996665</v>
       </c>
     </row>
     <row r="814">
@@ -6867,7 +6867,7 @@
         <v>813</v>
       </c>
       <c r="B814">
-        <v>110014756111</v>
+        <v>110015494026</v>
       </c>
     </row>
     <row r="815">
@@ -6875,7 +6875,7 @@
         <v>814</v>
       </c>
       <c r="B815">
-        <v>110071198049</v>
+        <v>110070413183</v>
       </c>
     </row>
     <row r="816">
@@ -6883,7 +6883,7 @@
         <v>815</v>
       </c>
       <c r="B816">
-        <v>110070573872</v>
+        <v>110065337317</v>
       </c>
     </row>
     <row r="817">
@@ -6891,7 +6891,7 @@
         <v>816</v>
       </c>
       <c r="B817">
-        <v>110019064377</v>
+        <v>110004047031</v>
       </c>
     </row>
     <row r="818">
@@ -6899,7 +6899,7 @@
         <v>817</v>
       </c>
       <c r="B818">
-        <v>110070813094</v>
+        <v>110056304994</v>
       </c>
     </row>
     <row r="819">
@@ -6907,7 +6907,7 @@
         <v>818</v>
       </c>
       <c r="B819">
-        <v>110071816639</v>
+        <v>110032019170</v>
       </c>
     </row>
     <row r="820">
@@ -6915,7 +6915,7 @@
         <v>819</v>
       </c>
       <c r="B820">
-        <v>110034112289</v>
+        <v>110070200653</v>
       </c>
     </row>
     <row r="821">
@@ -6923,7 +6923,7 @@
         <v>820</v>
       </c>
       <c r="B821">
-        <v>110022874273</v>
+        <v>110067603766</v>
       </c>
     </row>
     <row r="822">
@@ -6931,7 +6931,7 @@
         <v>821</v>
       </c>
       <c r="B822">
-        <v>110044754432</v>
+        <v>110001376261</v>
       </c>
     </row>
     <row r="823">
@@ -6939,7 +6939,7 @@
         <v>822</v>
       </c>
       <c r="B823">
-        <v>110058531227</v>
+        <v>110071642671</v>
       </c>
     </row>
     <row r="824">
@@ -6947,7 +6947,7 @@
         <v>823</v>
       </c>
       <c r="B824">
-        <v>110071861791</v>
+        <v>110020823732</v>
       </c>
     </row>
     <row r="825">
@@ -6955,7 +6955,7 @@
         <v>824</v>
       </c>
       <c r="B825">
-        <v>110044334654</v>
+        <v>110041048130</v>
       </c>
     </row>
     <row r="826">
@@ -6963,7 +6963,7 @@
         <v>825</v>
       </c>
       <c r="B826">
-        <v>110058921378</v>
+        <v>110072113291</v>
       </c>
     </row>
     <row r="827">
@@ -6971,7 +6971,7 @@
         <v>826</v>
       </c>
       <c r="B827">
-        <v>110071863035</v>
+        <v>110066308686</v>
       </c>
     </row>
     <row r="828">
@@ -6979,7 +6979,7 @@
         <v>827</v>
       </c>
       <c r="B828">
-        <v>110045983414</v>
+        <v>110029490352</v>
       </c>
     </row>
     <row r="829">
@@ -6987,7 +6987,7 @@
         <v>828</v>
       </c>
       <c r="B829">
-        <v>110070397764</v>
+        <v>110011414442</v>
       </c>
     </row>
     <row r="830">
@@ -6995,7 +6995,7 @@
         <v>829</v>
       </c>
       <c r="B830">
-        <v>110045248086</v>
+        <v>110070039291</v>
       </c>
     </row>
     <row r="831">
@@ -7003,7 +7003,7 @@
         <v>830</v>
       </c>
       <c r="B831">
-        <v>110037209053</v>
+        <v>110068884924</v>
       </c>
     </row>
     <row r="832">
@@ -7011,7 +7011,7 @@
         <v>831</v>
       </c>
       <c r="B832">
-        <v>110032642638</v>
+        <v>110070050651</v>
       </c>
     </row>
     <row r="833">
@@ -7019,7 +7019,7 @@
         <v>832</v>
       </c>
       <c r="B833">
-        <v>110037796953</v>
+        <v>110020746228</v>
       </c>
     </row>
     <row r="834">
@@ -7027,7 +7027,7 @@
         <v>833</v>
       </c>
       <c r="B834">
-        <v>110065457099</v>
+        <v>110059863045</v>
       </c>
     </row>
     <row r="835">
@@ -7035,7 +7035,7 @@
         <v>834</v>
       </c>
       <c r="B835">
-        <v>110046284917</v>
+        <v>110072004910</v>
       </c>
     </row>
     <row r="836">
@@ -7043,7 +7043,7 @@
         <v>835</v>
       </c>
       <c r="B836">
-        <v>110028211281</v>
+        <v>110070945259</v>
       </c>
     </row>
     <row r="837">
@@ -7051,7 +7051,7 @@
         <v>836</v>
       </c>
       <c r="B837">
-        <v>110019037941</v>
+        <v>110044346730</v>
       </c>
     </row>
     <row r="838">
@@ -7059,7 +7059,7 @@
         <v>837</v>
       </c>
       <c r="B838">
-        <v>110065107814</v>
+        <v>110070344655</v>
       </c>
     </row>
     <row r="839">
@@ -7067,7 +7067,7 @@
         <v>838</v>
       </c>
       <c r="B839">
-        <v>110030506370</v>
+        <v>110039334486</v>
       </c>
     </row>
     <row r="840">
@@ -7075,7 +7075,7 @@
         <v>839</v>
       </c>
       <c r="B840">
-        <v>110041317937</v>
+        <v>110070683725</v>
       </c>
     </row>
     <row r="841">
@@ -7083,7 +7083,7 @@
         <v>840</v>
       </c>
       <c r="B841">
-        <v>110064964800</v>
+        <v>110070365667</v>
       </c>
     </row>
     <row r="842">
@@ -7091,7 +7091,7 @@
         <v>841</v>
       </c>
       <c r="B842">
-        <v>110065341785</v>
+        <v>110018529412</v>
       </c>
     </row>
     <row r="843">
@@ -7099,7 +7099,7 @@
         <v>842</v>
       </c>
       <c r="B843">
-        <v>110044911398</v>
+        <v>110035187641</v>
       </c>
     </row>
     <row r="844">
@@ -7107,7 +7107,7 @@
         <v>843</v>
       </c>
       <c r="B844">
-        <v>110070616094</v>
+        <v>110071737740</v>
       </c>
     </row>
     <row r="845">
@@ -7115,7 +7115,7 @@
         <v>844</v>
       </c>
       <c r="B845">
-        <v>110046347707</v>
+        <v>110056192016</v>
       </c>
     </row>
     <row r="846">
@@ -7123,7 +7123,7 @@
         <v>845</v>
       </c>
       <c r="B846">
-        <v>110030661282</v>
+        <v>110034424692</v>
       </c>
     </row>
     <row r="847">
@@ -7131,7 +7131,7 @@
         <v>846</v>
       </c>
       <c r="B847">
-        <v>110001905109</v>
+        <v>110013463983</v>
       </c>
     </row>
     <row r="848">
@@ -7139,7 +7139,7 @@
         <v>847</v>
       </c>
       <c r="B848">
-        <v>110003377088</v>
+        <v>110068529097</v>
       </c>
     </row>
     <row r="849">
@@ -7147,7 +7147,7 @@
         <v>848</v>
       </c>
       <c r="B849">
-        <v>110044729684</v>
+        <v>110041404423</v>
       </c>
     </row>
     <row r="850">
@@ -7155,7 +7155,7 @@
         <v>849</v>
       </c>
       <c r="B850">
-        <v>110018449669</v>
+        <v>110015331149</v>
       </c>
     </row>
     <row r="851">
@@ -7163,7 +7163,7 @@
         <v>850</v>
       </c>
       <c r="B851">
-        <v>110068110314</v>
+        <v>110071346513</v>
       </c>
     </row>
     <row r="852">
@@ -7171,7 +7171,7 @@
         <v>851</v>
       </c>
       <c r="B852">
-        <v>110022741238</v>
+        <v>110070613230</v>
       </c>
     </row>
     <row r="853">
@@ -7179,7 +7179,7 @@
         <v>852</v>
       </c>
       <c r="B853">
-        <v>110069232020</v>
+        <v>110019147350</v>
       </c>
     </row>
     <row r="854">
@@ -7187,7 +7187,7 @@
         <v>853</v>
       </c>
       <c r="B854">
-        <v>110070334589</v>
+        <v>110071023081</v>
       </c>
     </row>
     <row r="855">
@@ -7195,7 +7195,7 @@
         <v>854</v>
       </c>
       <c r="B855">
-        <v>110070419573</v>
+        <v>110071902281</v>
       </c>
     </row>
     <row r="856">
@@ -7203,7 +7203,7 @@
         <v>855</v>
       </c>
       <c r="B856">
-        <v>110064384955</v>
+        <v>110034204359</v>
       </c>
     </row>
     <row r="857">
@@ -7211,7 +7211,7 @@
         <v>856</v>
       </c>
       <c r="B857">
-        <v>110034592947</v>
+        <v>110022932157</v>
       </c>
     </row>
     <row r="858">
@@ -7219,7 +7219,7 @@
         <v>857</v>
       </c>
       <c r="B858">
-        <v>110032434587</v>
+        <v>110044976657</v>
       </c>
     </row>
     <row r="859">
@@ -7227,7 +7227,7 @@
         <v>858</v>
       </c>
       <c r="B859">
-        <v>110066026071</v>
+        <v>110058731412</v>
       </c>
     </row>
     <row r="860">
@@ -7235,7 +7235,7 @@
         <v>859</v>
       </c>
       <c r="B860">
-        <v>110014198867</v>
+        <v>110071921981</v>
       </c>
     </row>
     <row r="861">
@@ -7243,7 +7243,7 @@
         <v>860</v>
       </c>
       <c r="B861">
-        <v>110045104169</v>
+        <v>110044519937</v>
       </c>
     </row>
     <row r="862">
@@ -7251,7 +7251,7 @@
         <v>861</v>
       </c>
       <c r="B862">
-        <v>110007035136</v>
+        <v>110059815927</v>
       </c>
     </row>
     <row r="863">
@@ -7259,7 +7259,7 @@
         <v>862</v>
       </c>
       <c r="B863">
-        <v>110070088777</v>
+        <v>110071922753</v>
       </c>
     </row>
     <row r="864">
@@ -7267,7 +7267,7 @@
         <v>863</v>
       </c>
       <c r="B864">
-        <v>110070410489</v>
+        <v>110046316697</v>
       </c>
     </row>
     <row r="865">
@@ -7275,7 +7275,7 @@
         <v>864</v>
       </c>
       <c r="B865">
-        <v>110010766652</v>
+        <v>110070400540</v>
       </c>
     </row>
     <row r="866">
@@ -7283,7 +7283,7 @@
         <v>865</v>
       </c>
       <c r="B866">
-        <v>110042273081</v>
+        <v>110045435971</v>
       </c>
     </row>
     <row r="867">
@@ -7291,7 +7291,7 @@
         <v>866</v>
       </c>
       <c r="B867">
-        <v>110070899216</v>
+        <v>110037363723</v>
       </c>
     </row>
     <row r="868">
@@ -7299,7 +7299,7 @@
         <v>867</v>
       </c>
       <c r="B868">
-        <v>110036249379</v>
+        <v>110032767049</v>
       </c>
     </row>
     <row r="869">
@@ -7307,7 +7307,7 @@
         <v>868</v>
       </c>
       <c r="B869">
-        <v>110066268531</v>
+        <v>110037910455</v>
       </c>
     </row>
     <row r="870">
@@ -7315,7 +7315,7 @@
         <v>869</v>
       </c>
       <c r="B870">
-        <v>110019545839</v>
+        <v>110065513796</v>
       </c>
     </row>
     <row r="871">
@@ -7323,7 +7323,7 @@
         <v>870</v>
       </c>
       <c r="B871">
-        <v>110071826998</v>
+        <v>110046493996</v>
       </c>
     </row>
     <row r="872">
@@ -7331,7 +7331,7 @@
         <v>871</v>
       </c>
       <c r="B872">
-        <v>110018054905</v>
+        <v>110028238770</v>
       </c>
     </row>
     <row r="873">
@@ -7339,7 +7339,7 @@
         <v>872</v>
       </c>
       <c r="B873">
-        <v>110016753235</v>
+        <v>110019120734</v>
       </c>
     </row>
     <row r="874">
@@ -7347,7 +7347,7 @@
         <v>873</v>
       </c>
       <c r="B874">
-        <v>110070708870</v>
+        <v>110065160907</v>
       </c>
     </row>
     <row r="875">
@@ -7355,7 +7355,7 @@
         <v>874</v>
       </c>
       <c r="B875">
-        <v>110033878668</v>
+        <v>110030528463</v>
       </c>
     </row>
     <row r="876">
@@ -7363,7 +7363,7 @@
         <v>875</v>
       </c>
       <c r="B876">
-        <v>110035318698</v>
+        <v>110041452549</v>
       </c>
     </row>
     <row r="877">
@@ -7371,7 +7371,7 @@
         <v>876</v>
       </c>
       <c r="B877">
-        <v>110009270136</v>
+        <v>110065025804</v>
       </c>
     </row>
     <row r="878">
@@ -7379,7 +7379,7 @@
         <v>877</v>
       </c>
       <c r="B878">
-        <v>110018384728</v>
+        <v>110072110095</v>
       </c>
     </row>
     <row r="879">
@@ -7387,7 +7387,7 @@
         <v>878</v>
       </c>
       <c r="B879">
-        <v>110071089688</v>
+        <v>110065405662</v>
       </c>
     </row>
     <row r="880">
@@ -7395,7 +7395,7 @@
         <v>879</v>
       </c>
       <c r="B880">
-        <v>110071090181</v>
+        <v>110045095400</v>
       </c>
     </row>
     <row r="881">
@@ -7403,7 +7403,7 @@
         <v>880</v>
       </c>
       <c r="B881">
-        <v>110046346263</v>
+        <v>110070710161</v>
       </c>
     </row>
     <row r="882">
@@ -7411,7 +7411,7 @@
         <v>881</v>
       </c>
       <c r="B882">
-        <v>110038899831</v>
+        <v>110046523188</v>
       </c>
     </row>
     <row r="883">
@@ -7419,7 +7419,7 @@
         <v>882</v>
       </c>
       <c r="B883">
-        <v>110058680182</v>
+        <v>110030681091</v>
       </c>
     </row>
     <row r="884">
@@ -7427,7 +7427,7 @@
         <v>883</v>
       </c>
       <c r="B884">
-        <v>110070229642</v>
+        <v>110001921109</v>
       </c>
     </row>
     <row r="885">
@@ -7435,7 +7435,7 @@
         <v>884</v>
       </c>
       <c r="B885">
-        <v>110005721914</v>
+        <v>110003427159</v>
       </c>
     </row>
     <row r="886">
@@ -7443,7 +7443,7 @@
         <v>885</v>
       </c>
       <c r="B886">
-        <v>110032651486</v>
+        <v>110044958016</v>
       </c>
     </row>
     <row r="887">
@@ -7451,7 +7451,7 @@
         <v>886</v>
       </c>
       <c r="B887">
-        <v>110046119945</v>
+        <v>110018577556</v>
       </c>
     </row>
     <row r="888">
@@ -7459,7 +7459,7 @@
         <v>887</v>
       </c>
       <c r="B888">
-        <v>110070469257</v>
+        <v>110068143351</v>
       </c>
     </row>
     <row r="889">
@@ -7467,7 +7467,7 @@
         <v>888</v>
       </c>
       <c r="B889">
-        <v>110038335744</v>
+        <v>110022767692</v>
       </c>
     </row>
     <row r="890">
@@ -7475,7 +7475,7 @@
         <v>889</v>
       </c>
       <c r="B890">
-        <v>110071202325</v>
+        <v>110069162033</v>
       </c>
     </row>
     <row r="891">
@@ -7483,7 +7483,7 @@
         <v>890</v>
       </c>
       <c r="B891">
-        <v>110001047956</v>
+        <v>110070335012</v>
       </c>
     </row>
     <row r="892">
@@ -7491,7 +7491,7 @@
         <v>891</v>
       </c>
       <c r="B892">
-        <v>110045130407</v>
+        <v>110070426307</v>
       </c>
     </row>
     <row r="893">
@@ -7499,7 +7499,7 @@
         <v>892</v>
       </c>
       <c r="B893">
-        <v>110004689230</v>
+        <v>110064475919</v>
       </c>
     </row>
     <row r="894">
@@ -7507,7 +7507,7 @@
         <v>893</v>
       </c>
       <c r="B894">
-        <v>110067206071</v>
+        <v>110034646578</v>
       </c>
     </row>
     <row r="895">
@@ -7515,7 +7515,7 @@
         <v>894</v>
       </c>
       <c r="B895">
-        <v>110005193389</v>
+        <v>110032456349</v>
       </c>
     </row>
     <row r="896">
@@ -7523,7 +7523,7 @@
         <v>895</v>
       </c>
       <c r="B896">
-        <v>110004921363</v>
+        <v>110071981075</v>
       </c>
     </row>
     <row r="897">
@@ -7531,7 +7531,7 @@
         <v>896</v>
       </c>
       <c r="B897">
-        <v>110002869496</v>
+        <v>110066091552</v>
       </c>
     </row>
     <row r="898">
@@ -7539,7 +7539,7 @@
         <v>897</v>
       </c>
       <c r="B898">
-        <v>110040897250</v>
+        <v>110014273990</v>
       </c>
     </row>
     <row r="899">
@@ -7547,7 +7547,7 @@
         <v>898</v>
       </c>
       <c r="B899">
-        <v>110070675962</v>
+        <v>110045235615</v>
       </c>
     </row>
     <row r="900">
@@ -7555,7 +7555,7 @@
         <v>899</v>
       </c>
       <c r="B900">
-        <v>110043520375</v>
+        <v>110007395167</v>
       </c>
     </row>
     <row r="901">
@@ -7563,7 +7563,7 @@
         <v>900</v>
       </c>
       <c r="B901">
-        <v>110008016672</v>
+        <v>110072130262</v>
       </c>
     </row>
     <row r="902">
@@ -7571,7 +7571,7 @@
         <v>901</v>
       </c>
       <c r="B902">
-        <v>110036163022</v>
+        <v>110070067211</v>
       </c>
     </row>
     <row r="903">
@@ -7579,7 +7579,7 @@
         <v>902</v>
       </c>
       <c r="B903">
-        <v>110070695196</v>
+        <v>110070416666</v>
       </c>
     </row>
     <row r="904">
@@ -7587,7 +7587,7 @@
         <v>903</v>
       </c>
       <c r="B904">
-        <v>110063678284</v>
+        <v>110011110314</v>
       </c>
     </row>
     <row r="905">
@@ -7595,7 +7595,7 @@
         <v>904</v>
       </c>
       <c r="B905">
-        <v>110005452063</v>
+        <v>110042561714</v>
       </c>
     </row>
     <row r="906">
@@ -7603,7 +7603,7 @@
         <v>905</v>
       </c>
       <c r="B906">
-        <v>110031805232</v>
+        <v>110071133611</v>
       </c>
     </row>
     <row r="907">
@@ -7611,7 +7611,7 @@
         <v>906</v>
       </c>
       <c r="B907">
-        <v>110071817627</v>
+        <v>110036323298</v>
       </c>
     </row>
     <row r="908">
@@ -7619,7 +7619,7 @@
         <v>907</v>
       </c>
       <c r="B908">
-        <v>110070560392</v>
+        <v>110066333827</v>
       </c>
     </row>
     <row r="909">
@@ -7627,7 +7627,7 @@
         <v>908</v>
       </c>
       <c r="B909">
-        <v>110065120309</v>
+        <v>110019628526</v>
       </c>
     </row>
     <row r="910">
@@ -7635,7 +7635,7 @@
         <v>909</v>
       </c>
       <c r="B910">
-        <v>110070222425</v>
+        <v>110071911752</v>
       </c>
     </row>
     <row r="911">
@@ -7643,7 +7643,7 @@
         <v>910</v>
       </c>
       <c r="B911">
-        <v>110001716153</v>
+        <v>110018185890</v>
       </c>
     </row>
     <row r="912">
@@ -7651,7 +7651,7 @@
         <v>911</v>
       </c>
       <c r="B912">
-        <v>110070582219</v>
+        <v>110016915891</v>
       </c>
     </row>
     <row r="913">
@@ -7659,7 +7659,7 @@
         <v>912</v>
       </c>
       <c r="B913">
-        <v>110006409813</v>
+        <v>110070915304</v>
       </c>
     </row>
     <row r="914">
@@ -7667,7 +7667,7 @@
         <v>913</v>
       </c>
       <c r="B914">
-        <v>110037766520</v>
+        <v>110033929202</v>
       </c>
     </row>
     <row r="915">
@@ -7675,7 +7675,7 @@
         <v>914</v>
       </c>
       <c r="B915">
-        <v>110070457512</v>
+        <v>110035384704</v>
       </c>
     </row>
     <row r="916">
@@ -7683,7 +7683,7 @@
         <v>915</v>
       </c>
       <c r="B916">
-        <v>110070427838</v>
+        <v>110009612115</v>
       </c>
     </row>
     <row r="917">
@@ -7691,7 +7691,7 @@
         <v>916</v>
       </c>
       <c r="B917">
-        <v>110070698859</v>
+        <v>110018505713</v>
       </c>
     </row>
     <row r="918">
@@ -7699,7 +7699,7 @@
         <v>917</v>
       </c>
       <c r="B918">
-        <v>110016852495</v>
+        <v>110071251405</v>
       </c>
     </row>
     <row r="919">
@@ -7707,7 +7707,7 @@
         <v>918</v>
       </c>
       <c r="B919">
-        <v>110019316079</v>
+        <v>110071252449</v>
       </c>
     </row>
     <row r="920">
@@ -7715,7 +7715,7 @@
         <v>919</v>
       </c>
       <c r="B920">
-        <v>110033883616</v>
+        <v>110046522269</v>
       </c>
     </row>
     <row r="921">
@@ -7723,7 +7723,7 @@
         <v>920</v>
       </c>
       <c r="B921">
-        <v>110012595557</v>
+        <v>110039237554</v>
       </c>
     </row>
     <row r="922">
@@ -7731,7 +7731,7 @@
         <v>921</v>
       </c>
       <c r="B922">
-        <v>110056109063</v>
+        <v>110058884658</v>
       </c>
     </row>
     <row r="923">
@@ -7739,7 +7739,7 @@
         <v>922</v>
       </c>
       <c r="B923">
-        <v>110070579275</v>
+        <v>110070224792</v>
       </c>
     </row>
     <row r="924">
@@ -7747,7 +7747,7 @@
         <v>923</v>
       </c>
       <c r="B924">
-        <v>110068193706</v>
+        <v>110005920995</v>
       </c>
     </row>
     <row r="925">
@@ -7755,7 +7755,7 @@
         <v>924</v>
       </c>
       <c r="B925">
-        <v>110020769239</v>
+        <v>110032811330</v>
       </c>
     </row>
     <row r="926">
@@ -7763,7 +7763,7 @@
         <v>925</v>
       </c>
       <c r="B926">
-        <v>110031687020</v>
+        <v>110046385014</v>
       </c>
     </row>
     <row r="927">
@@ -7771,7 +7771,7 @@
         <v>926</v>
       </c>
       <c r="B927">
-        <v>110067966302</v>
+        <v>110070484281</v>
       </c>
     </row>
     <row r="928">
@@ -7779,7 +7779,7 @@
         <v>927</v>
       </c>
       <c r="B928">
-        <v>110011987083</v>
+        <v>110038710730</v>
       </c>
     </row>
     <row r="929">
@@ -7787,7 +7787,7 @@
         <v>928</v>
       </c>
       <c r="B929">
-        <v>110038451403</v>
+        <v>110071347778</v>
       </c>
     </row>
     <row r="930">
@@ -7795,7 +7795,7 @@
         <v>929</v>
       </c>
       <c r="B930">
-        <v>110003676344</v>
+        <v>110001019068</v>
       </c>
     </row>
     <row r="931">
@@ -7803,7 +7803,7 @@
         <v>930</v>
       </c>
       <c r="B931">
-        <v>110046515311</v>
+        <v>110045264691</v>
       </c>
     </row>
     <row r="932">
@@ -7811,7 +7811,7 @@
         <v>931</v>
       </c>
       <c r="B932">
-        <v>110003130200</v>
+        <v>110004808762</v>
       </c>
     </row>
     <row r="933">
@@ -7819,7 +7819,7 @@
         <v>932</v>
       </c>
       <c r="B933">
-        <v>110070471983</v>
+        <v>110067575948</v>
       </c>
     </row>
     <row r="934">
@@ -7827,7 +7827,7 @@
         <v>933</v>
       </c>
       <c r="B934">
-        <v>110040420247</v>
+        <v>110005414006</v>
       </c>
     </row>
     <row r="935">
@@ -7835,7 +7835,7 @@
         <v>934</v>
       </c>
       <c r="B935">
-        <v>110065598428</v>
+        <v>110072141576</v>
       </c>
     </row>
     <row r="936">
@@ -7843,7 +7843,7 @@
         <v>935</v>
       </c>
       <c r="B936">
-        <v>110065216778</v>
+        <v>110005215310</v>
       </c>
     </row>
     <row r="937">
@@ -7851,7 +7851,7 @@
         <v>936</v>
       </c>
       <c r="B937">
-        <v>110037757647</v>
+        <v>110002883657</v>
       </c>
     </row>
     <row r="938">
@@ -7859,7 +7859,7 @@
         <v>937</v>
       </c>
       <c r="B938">
-        <v>110024991366</v>
+        <v>110041250008</v>
       </c>
     </row>
     <row r="939">
@@ -7867,7 +7867,7 @@
         <v>938</v>
       </c>
       <c r="B939">
-        <v>110070463405</v>
+        <v>110070831638</v>
       </c>
     </row>
     <row r="940">
@@ -7875,7 +7875,7 @@
         <v>939</v>
       </c>
       <c r="B940">
-        <v>110003771525</v>
+        <v>110043766314</v>
       </c>
     </row>
     <row r="941">
@@ -7883,7 +7883,7 @@
         <v>940</v>
       </c>
       <c r="B941">
-        <v>110042280910</v>
+        <v>110008341142</v>
       </c>
     </row>
     <row r="942">
@@ -7891,7 +7891,7 @@
         <v>941</v>
       </c>
       <c r="B942">
-        <v>110065868760</v>
+        <v>110036233812</v>
       </c>
     </row>
     <row r="943">
@@ -7899,7 +7899,7 @@
         <v>942</v>
       </c>
       <c r="B943">
-        <v>110070332567</v>
+        <v>110070868987</v>
       </c>
     </row>
     <row r="944">
@@ -7907,7 +7907,7 @@
         <v>943</v>
       </c>
       <c r="B944">
-        <v>110059767612</v>
+        <v>110063831723</v>
       </c>
     </row>
     <row r="945">
@@ -7915,7 +7915,7 @@
         <v>944</v>
       </c>
       <c r="B945">
-        <v>110066332356</v>
+        <v>110005614399</v>
       </c>
     </row>
     <row r="946">
@@ -7923,7 +7923,7 @@
         <v>945</v>
       </c>
       <c r="B946">
-        <v>110056975000</v>
+        <v>110031828752</v>
       </c>
     </row>
     <row r="947">
@@ -7931,7 +7931,7 @@
         <v>946</v>
       </c>
       <c r="B947">
-        <v>110071145725</v>
+        <v>110071903705</v>
       </c>
     </row>
     <row r="948">
@@ -7939,7 +7939,7 @@
         <v>947</v>
       </c>
       <c r="B948">
-        <v>110063864073</v>
+        <v>110070601516</v>
       </c>
     </row>
     <row r="949">
@@ -7947,7 +7947,7 @@
         <v>948</v>
       </c>
       <c r="B949">
-        <v>110071089173</v>
+        <v>110065174885</v>
       </c>
     </row>
     <row r="950">
@@ -7955,7 +7955,7 @@
         <v>949</v>
       </c>
       <c r="B950">
-        <v>110018347788</v>
+        <v>110070217694</v>
       </c>
     </row>
     <row r="951">
@@ -7963,7 +7963,7 @@
         <v>950</v>
       </c>
       <c r="B951">
-        <v>110071338636</v>
+        <v>110001727052</v>
       </c>
     </row>
     <row r="952">
@@ -7971,7 +7971,7 @@
         <v>951</v>
       </c>
       <c r="B952">
-        <v>110001447220</v>
+        <v>110070640728</v>
       </c>
     </row>
     <row r="953">
@@ -7979,7 +7979,7 @@
         <v>952</v>
       </c>
       <c r="B953">
-        <v>110058421765</v>
+        <v>110006563897</v>
       </c>
     </row>
     <row r="954">
@@ -7987,7 +7987,7 @@
         <v>953</v>
       </c>
       <c r="B954">
-        <v>110046096194</v>
+        <v>110037847818</v>
       </c>
     </row>
     <row r="955">
@@ -7995,7 +7995,7 @@
         <v>954</v>
       </c>
       <c r="B955">
-        <v>110042645661</v>
+        <v>110070472043</v>
       </c>
     </row>
     <row r="956">
@@ -8003,7 +8003,7 @@
         <v>955</v>
       </c>
       <c r="B956">
-        <v>110040958755</v>
+        <v>110070437954</v>
       </c>
     </row>
     <row r="957">
@@ -8011,7 +8011,7 @@
         <v>956</v>
       </c>
       <c r="B957">
-        <v>110030893004</v>
+        <v>110070875402</v>
       </c>
     </row>
     <row r="958">
@@ -8019,7 +8019,7 @@
         <v>957</v>
       </c>
       <c r="B958">
-        <v>110019060406</v>
+        <v>110016944093</v>
       </c>
     </row>
     <row r="959">
@@ -8027,7 +8027,7 @@
         <v>958</v>
       </c>
       <c r="B959">
-        <v>110071826169</v>
+        <v>110019399186</v>
       </c>
     </row>
     <row r="960">
@@ -8035,7 +8035,7 @@
         <v>959</v>
       </c>
       <c r="B960">
-        <v>110021018030</v>
+        <v>110071968761</v>
       </c>
     </row>
     <row r="961">
@@ -8043,7 +8043,7 @@
         <v>960</v>
       </c>
       <c r="B961">
-        <v>110025404042</v>
+        <v>110033933787</v>
       </c>
     </row>
     <row r="962">
@@ -8051,7 +8051,7 @@
         <v>961</v>
       </c>
       <c r="B962">
-        <v>110071723254</v>
+        <v>110013152104</v>
       </c>
     </row>
     <row r="963">
@@ -8059,7 +8059,7 @@
         <v>962</v>
       </c>
       <c r="B963">
-        <v>110070700682</v>
+        <v>110056232928</v>
       </c>
     </row>
     <row r="964">
@@ -8067,7 +8067,7 @@
         <v>963</v>
       </c>
       <c r="B964">
-        <v>110032309990</v>
+        <v>110070627263</v>
       </c>
     </row>
     <row r="965">
@@ -8075,7 +8075,7 @@
         <v>964</v>
       </c>
       <c r="B965">
-        <v>110065020033</v>
+        <v>110068226342</v>
       </c>
     </row>
     <row r="966">
@@ -8083,7 +8083,7 @@
         <v>965</v>
       </c>
       <c r="B966">
-        <v>110070063489</v>
+        <v>110020889699</v>
       </c>
     </row>
     <row r="967">
@@ -8091,7 +8091,7 @@
         <v>966</v>
       </c>
       <c r="B967">
-        <v>110001255677</v>
+        <v>110031710584</v>
       </c>
     </row>
     <row r="968">
@@ -8099,7 +8099,7 @@
         <v>967</v>
       </c>
       <c r="B968">
-        <v>110002762626</v>
+        <v>110068005553</v>
       </c>
     </row>
     <row r="969">
@@ -8107,7 +8107,7 @@
         <v>968</v>
       </c>
       <c r="B969">
-        <v>110040280442</v>
+        <v>110012119037</v>
       </c>
     </row>
     <row r="970">
@@ -8115,7 +8115,7 @@
         <v>969</v>
       </c>
       <c r="B970">
-        <v>110071709598</v>
+        <v>110038755987</v>
       </c>
     </row>
     <row r="971">
@@ -8123,7 +8123,7 @@
         <v>970</v>
       </c>
       <c r="B971">
-        <v>110070541157</v>
+        <v>110003728048</v>
       </c>
     </row>
     <row r="972">
@@ -8131,7 +8131,7 @@
         <v>971</v>
       </c>
       <c r="B972">
-        <v>110002141334</v>
+        <v>110051772738</v>
       </c>
     </row>
     <row r="973">
@@ -8139,7 +8139,7 @@
         <v>972</v>
       </c>
       <c r="B973">
-        <v>110070669014</v>
+        <v>110003164566</v>
       </c>
     </row>
     <row r="974">
@@ -8147,7 +8147,7 @@
         <v>973</v>
       </c>
       <c r="B974">
-        <v>110003512057</v>
+        <v>110070487151</v>
       </c>
     </row>
     <row r="975">
@@ -8155,7 +8155,7 @@
         <v>974</v>
       </c>
       <c r="B975">
-        <v>110003362218</v>
+        <v>110040673107</v>
       </c>
     </row>
     <row r="976">
@@ -8163,7 +8163,7 @@
         <v>975</v>
       </c>
       <c r="B976">
-        <v>110054271612</v>
+        <v>110065655035</v>
       </c>
     </row>
     <row r="977">
@@ -8171,7 +8171,7 @@
         <v>976</v>
       </c>
       <c r="B977">
-        <v>110065184231</v>
+        <v>110065274349</v>
       </c>
     </row>
     <row r="978">
@@ -8179,7 +8179,7 @@
         <v>977</v>
       </c>
       <c r="B978">
-        <v>110018806568</v>
+        <v>110037831825</v>
       </c>
     </row>
     <row r="979">
@@ -8187,7 +8187,7 @@
         <v>978</v>
       </c>
       <c r="B979">
-        <v>110005486875</v>
+        <v>110025021036</v>
       </c>
     </row>
     <row r="980">
@@ -8195,7 +8195,7 @@
         <v>979</v>
       </c>
       <c r="B980">
-        <v>110066337093</v>
+        <v>110070478174</v>
       </c>
     </row>
     <row r="981">
@@ -8203,7 +8203,7 @@
         <v>980</v>
       </c>
       <c r="B981">
-        <v>110070275971</v>
+        <v>110003844626</v>
       </c>
     </row>
     <row r="982">
@@ -8211,7 +8211,7 @@
         <v>981</v>
       </c>
       <c r="B982">
-        <v>110070306842</v>
+        <v>110042572418</v>
       </c>
     </row>
     <row r="983">
@@ -8219,7 +8219,7 @@
         <v>982</v>
       </c>
       <c r="B983">
-        <v>110041973834</v>
+        <v>110065936161</v>
       </c>
     </row>
     <row r="984">
@@ -8227,7 +8227,7 @@
         <v>983</v>
       </c>
       <c r="B984">
-        <v>110017607133</v>
+        <v>110070332982</v>
       </c>
     </row>
     <row r="985">
@@ -8235,7 +8235,7 @@
         <v>984</v>
       </c>
       <c r="B985">
-        <v>110042783654</v>
+        <v>110060072237</v>
       </c>
     </row>
     <row r="986">
@@ -8243,7 +8243,7 @@
         <v>985</v>
       </c>
       <c r="B986">
-        <v>110017154988</v>
+        <v>110066403001</v>
       </c>
     </row>
     <row r="987">
@@ -8251,7 +8251,7 @@
         <v>986</v>
       </c>
       <c r="B987">
-        <v>110022454967</v>
+        <v>110057109267</v>
       </c>
     </row>
     <row r="988">
@@ -8259,7 +8259,7 @@
         <v>987</v>
       </c>
       <c r="B988">
-        <v>110065157733</v>
+        <v>110071296769</v>
       </c>
     </row>
     <row r="989">
@@ -8267,7 +8267,7 @@
         <v>988</v>
       </c>
       <c r="B989">
-        <v>110029980821</v>
+        <v>110064011769</v>
       </c>
     </row>
     <row r="990">
@@ -8275,7 +8275,7 @@
         <v>989</v>
       </c>
       <c r="B990">
-        <v>110070436324</v>
+        <v>110071248778</v>
       </c>
     </row>
     <row r="991">
@@ -8283,7 +8283,7 @@
         <v>990</v>
       </c>
       <c r="B991">
-        <v>110070343407</v>
+        <v>110018461449</v>
       </c>
     </row>
     <row r="992">
@@ -8291,7 +8291,7 @@
         <v>991</v>
       </c>
       <c r="B992">
-        <v>110001871298</v>
+        <v>110071482316</v>
       </c>
     </row>
     <row r="993">
@@ -8299,7 +8299,7 @@
         <v>992</v>
       </c>
       <c r="B993">
-        <v>110044235440</v>
+        <v>110001449521</v>
       </c>
     </row>
     <row r="994">
@@ -8307,7 +8307,7 @@
         <v>993</v>
       </c>
       <c r="B994">
-        <v>110066382355</v>
+        <v>110058619623</v>
       </c>
     </row>
     <row r="995">
@@ -8315,7 +8315,7 @@
         <v>994</v>
       </c>
       <c r="B995">
-        <v>110070343699</v>
+        <v>110046351354</v>
       </c>
     </row>
     <row r="996">
@@ -8323,7 +8323,7 @@
         <v>995</v>
       </c>
       <c r="B996">
-        <v>110018191801</v>
+        <v>110043082357</v>
       </c>
     </row>
     <row r="997">
@@ -8331,7 +8331,7 @@
         <v>996</v>
       </c>
       <c r="B997">
-        <v>110032176302</v>
+        <v>110041319917</v>
       </c>
     </row>
     <row r="998">
@@ -8339,7 +8339,7 @@
         <v>997</v>
       </c>
       <c r="B998">
-        <v>110000508031</v>
+        <v>110030926568</v>
       </c>
     </row>
     <row r="999">
@@ -8347,7 +8347,7 @@
         <v>998</v>
       </c>
       <c r="B999">
-        <v>110002624722</v>
+        <v>110019143434</v>
       </c>
     </row>
     <row r="1000">
@@ -8355,7 +8355,7 @@
         <v>999</v>
       </c>
       <c r="B1000">
-        <v>110071783410</v>
+        <v>110071911357</v>
       </c>
     </row>
     <row r="1001">
@@ -8363,7 +8363,7 @@
         <v>1000</v>
       </c>
       <c r="B1001">
-        <v>110066201782</v>
+        <v>110021116683</v>
       </c>
     </row>
   </sheetData>
